--- a/results/tables/07_geographic_economic_profiles.xlsx
+++ b/results/tables/07_geographic_economic_profiles.xlsx
@@ -1427,25 +1427,25 @@
         <v>2306903683.856934</v>
       </c>
       <c r="U2" t="n">
-        <v>87546.28125</v>
+        <v>87546.28094094961</v>
       </c>
       <c r="V2" t="n">
-        <v>56389233.31388132</v>
+        <v>56389233.3156792</v>
       </c>
       <c r="W2" t="n">
-        <v>19950380.594001</v>
+        <v>19950380.59541911</v>
       </c>
       <c r="X2" t="n">
-        <v>76427160.18913235</v>
+        <v>76427160.19203925</v>
       </c>
       <c r="Y2" t="n">
-        <v>577583884</v>
+        <v>577583886</v>
       </c>
       <c r="Z2" t="n">
-        <v>654011044.1891322</v>
+        <v>654011046.1920393</v>
       </c>
       <c r="AA2" t="n">
-        <v>2960914728.046066</v>
+        <v>2960914730.048973</v>
       </c>
       <c r="AB2" t="n">
         <v>3030790</v>
@@ -1491,190 +1491,190 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>87546.28125</v>
+        <v>87546.2809409496</v>
       </c>
       <c r="AT2" t="n">
-        <v>87546.28125</v>
+        <v>87546.2809409496</v>
       </c>
       <c r="AU2" t="n">
-        <v>87546.28125</v>
+        <v>87546.2809409496</v>
       </c>
       <c r="AV2" t="n">
-        <v>23876.25852272728</v>
+        <v>23876.2584384408</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.638069759972638e-12</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>23876.25852272727</v>
+        <v>23876.2584384408</v>
       </c>
       <c r="AY2" t="n">
-        <v>23876.25852272727</v>
+        <v>23876.2584384408</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23876.25852272727</v>
+        <v>23876.2584384408</v>
       </c>
       <c r="BA2" t="n">
-        <v>50468800.91279141</v>
+        <v>50468800.8831956</v>
       </c>
       <c r="BB2" t="n">
-        <v>12615389.53306885</v>
+        <v>12615389.44182387</v>
       </c>
       <c r="BC2" t="n">
-        <v>42618557.64794922</v>
+        <v>42618557.60749198</v>
       </c>
       <c r="BD2" t="n">
-        <v>145459184.7977539</v>
+        <v>145459184.5049417</v>
       </c>
       <c r="BE2" t="n">
-        <v>15378881.81287673</v>
+        <v>15378881.81336705</v>
       </c>
       <c r="BF2" t="n">
-        <v>13764218.43076129</v>
+        <v>13764218.42268971</v>
       </c>
       <c r="BG2" t="n">
-        <v>3440560.781746049</v>
+        <v>3440560.756861056</v>
       </c>
       <c r="BH2" t="n">
-        <v>11623242.99489524</v>
+        <v>11623242.98386145</v>
       </c>
       <c r="BI2" t="n">
-        <v>39670686.76302378</v>
+        <v>39670686.68316592</v>
       </c>
       <c r="BJ2" t="n">
-        <v>24748815.97345254</v>
+        <v>24748815.97893379</v>
       </c>
       <c r="BK2" t="n">
-        <v>2513496.107384884</v>
+        <v>2513496.129149764</v>
       </c>
       <c r="BL2" t="n">
-        <v>12341710.87174749</v>
+        <v>12341710.77931686</v>
       </c>
       <c r="BM2" t="n">
-        <v>62385865.52671562</v>
+        <v>62385864.61526985</v>
       </c>
       <c r="BN2" t="n">
-        <v>5441012.889273</v>
+        <v>5441012.889659758</v>
       </c>
       <c r="BO2" t="n">
-        <v>6749677.083668875</v>
+        <v>6749677.085163761</v>
       </c>
       <c r="BP2" t="n">
-        <v>685498.9383776957</v>
+        <v>685498.9443135719</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3365921.146840225</v>
+        <v>3365921.121631871</v>
       </c>
       <c r="BR2" t="n">
-        <v>17014326.96183153</v>
+        <v>17014326.71325541</v>
       </c>
       <c r="BS2" t="n">
-        <v>56164637.51197238</v>
+        <v>56164637.48967049</v>
       </c>
       <c r="BT2" t="n">
-        <v>22918383.8131479</v>
+        <v>22918384.01761166</v>
       </c>
       <c r="BU2" t="n">
-        <v>62281317.80797935</v>
+        <v>62281318.19631388</v>
       </c>
       <c r="BV2" t="n">
-        <v>177550770.79082</v>
+        <v>177550770.0602665</v>
       </c>
       <c r="BW2" t="n">
-        <v>20843770.96067245</v>
+        <v>20843770.96146525</v>
       </c>
       <c r="BX2" t="n">
-        <v>15317628.4123561</v>
+        <v>15317628.40627377</v>
       </c>
       <c r="BY2" t="n">
-        <v>6250468.3126767</v>
+        <v>6250468.368439543</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16985813.94763073</v>
+        <v>16985814.05354015</v>
       </c>
       <c r="CA2" t="n">
-        <v>48422937.48840547</v>
+        <v>48422937.28916359</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>577583884</v>
+        <v>577583886</v>
       </c>
       <c r="CD2" t="n">
-        <v>577583884</v>
+        <v>577583886</v>
       </c>
       <c r="CE2" t="n">
-        <v>577583884</v>
+        <v>577583886</v>
       </c>
       <c r="CF2" t="n">
-        <v>157522877.4545455</v>
+        <v>157522878</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.980306747369585e-08</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>157522877.4545454</v>
+        <v>157522878</v>
       </c>
       <c r="CI2" t="n">
-        <v>157522877.4545454</v>
+        <v>157522878</v>
       </c>
       <c r="CJ2" t="n">
-        <v>157522877.4545454</v>
+        <v>157522878</v>
       </c>
       <c r="CK2" t="n">
-        <v>56164637.51197238</v>
+        <v>56164637.48967049</v>
       </c>
       <c r="CL2" t="n">
-        <v>600502267.8131479</v>
+        <v>600502270.0176116</v>
       </c>
       <c r="CM2" t="n">
-        <v>639865201.8079793</v>
+        <v>639865204.1963139</v>
       </c>
       <c r="CN2" t="n">
-        <v>755134654.79082</v>
+        <v>755134656.0602665</v>
       </c>
       <c r="CO2" t="n">
-        <v>178366648.4152179</v>
+        <v>178366648.9614652</v>
       </c>
       <c r="CP2" t="n">
-        <v>15317628.4123561</v>
+        <v>15317628.40627377</v>
       </c>
       <c r="CQ2" t="n">
-        <v>163773345.7672222</v>
+        <v>163773346.3684395</v>
       </c>
       <c r="CR2" t="n">
-        <v>174508691.4021762</v>
+        <v>174508692.0535401</v>
       </c>
       <c r="CS2" t="n">
-        <v>205945814.9429509</v>
+        <v>205945815.2891636</v>
       </c>
       <c r="CT2" t="n">
-        <v>56164637.51197238</v>
+        <v>56164637.48967049</v>
       </c>
       <c r="CU2" t="n">
-        <v>2907405951.670082</v>
+        <v>2907405953.874545</v>
       </c>
       <c r="CV2" t="n">
-        <v>2946768885.664913</v>
+        <v>2946768888.053247</v>
       </c>
       <c r="CW2" t="n">
-        <v>3062038338.647754</v>
+        <v>3062038339.9172</v>
       </c>
       <c r="CX2" t="n">
-        <v>807522198.558018</v>
+        <v>807522199.1042653</v>
       </c>
       <c r="CY2" t="n">
-        <v>15317628.4123561</v>
+        <v>15317628.40627376</v>
       </c>
       <c r="CZ2" t="n">
-        <v>792928895.9100221</v>
+        <v>792928896.5112395</v>
       </c>
       <c r="DA2" t="n">
-        <v>803664241.5449762</v>
+        <v>803664242.1963402</v>
       </c>
       <c r="DB2" t="n">
-        <v>835101365.0857509</v>
+        <v>835101365.4319636</v>
       </c>
       <c r="DC2" t="n">
         <v>1290880764850.778</v>
@@ -1710,91 +1710,91 @@
         <v>0.7843188022779657</v>
       </c>
       <c r="DN2" t="n">
-        <v>365946026167.9985</v>
+        <v>365946027314.0111</v>
       </c>
       <c r="DO2" t="n">
-        <v>179108512762.1163</v>
+        <v>179108513180.8092</v>
       </c>
       <c r="DP2" t="n">
-        <v>142434692345.7762</v>
+        <v>142434693524.5155</v>
       </c>
       <c r="DQ2" t="n">
-        <v>332071141080.5703</v>
+        <v>332071140228.8774</v>
       </c>
       <c r="DR2" t="n">
-        <v>681676136365.0035</v>
+        <v>681676141321.8163</v>
       </c>
       <c r="DS2" t="n">
-        <v>241.9962845115741</v>
+        <v>241.9962852694203</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.122464829496134</v>
+        <v>0.1224648298796502</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.05993914924122998</v>
+        <v>0.0599391493813467</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.04766615584029307</v>
+        <v>0.04766615623476139</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1111285073890904</v>
+        <v>0.1111285071040691</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2281247666102512</v>
+        <v>0.228124768269062</v>
       </c>
       <c r="DY2" t="n">
-        <v>1656826791018.777</v>
+        <v>1656826792164.789</v>
       </c>
       <c r="DZ2" t="n">
-        <v>796144303486.1973</v>
+        <v>796144303909.7048</v>
       </c>
       <c r="EA2" t="n">
-        <v>652259745642.3323</v>
+        <v>652259745362.9189</v>
       </c>
       <c r="EB2" t="n">
-        <v>1502191019398.516</v>
+        <v>1502191022700.372</v>
       </c>
       <c r="EC2" t="n">
-        <v>3011692437429.716</v>
+        <v>3011692440495.9</v>
       </c>
       <c r="ED2" t="n">
-        <v>1095.642250045126</v>
+        <v>1095.642250802972</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.5544615761822554</v>
+        <v>0.5544615765657716</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.26643184898528</v>
+        <v>0.266431849127008</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2182804917264197</v>
+        <v>0.2182804916329132</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.5027122960936541</v>
+        <v>0.5027122971986291</v>
       </c>
       <c r="EI2" t="n">
-        <v>1.007871036903419</v>
+        <v>1.007871037929526</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.7793809442185274</v>
+        <v>0.7793809436626616</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01389119799367201</v>
+        <v>0.01389119801236688</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.7533882425602821</v>
+        <v>0.7533882409035392</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.7828587079604467</v>
+        <v>0.7828587071464301</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.7934577122131101</v>
+        <v>0.7934577136093095</v>
       </c>
       <c r="EO2" t="n">
         <v>1.535787001913825</v>
       </c>
       <c r="EP2" t="n">
-        <v>2.220501562483299e-16</v>
+        <v>0</v>
       </c>
       <c r="EQ2" t="n">
         <v>1.535787001913825</v>
@@ -1806,25 +1806,25 @@
         <v>1.535787001913825</v>
       </c>
       <c r="ET2" t="n">
-        <v>1.971185179914242</v>
+        <v>1.971185181247648</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.03739077659015008</v>
+        <v>0.03739077657530292</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.935562503587696</v>
+        <v>1.935562505055285</v>
       </c>
       <c r="EW2" t="n">
-        <v>1.961767794605907</v>
+        <v>1.961767796195906</v>
       </c>
       <c r="EX2" t="n">
-        <v>2.038506727768815</v>
+        <v>2.03850672861393</v>
       </c>
       <c r="EY2" t="n">
         <v>1.535787001913825</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1.971185179914242</v>
+        <v>1.971185181247648</v>
       </c>
       <c r="FA2" t="n">
         <v>0.4512570444911349</v>
@@ -1989,25 +1989,25 @@
         <v>5881876834.994995</v>
       </c>
       <c r="U3" t="n">
-        <v>14892693.39476776</v>
+        <v>14892693.68263882</v>
       </c>
       <c r="V3" t="n">
-        <v>22417638.84952198</v>
+        <v>22417638.84812267</v>
       </c>
       <c r="W3" t="n">
-        <v>23569385.61679937</v>
+        <v>23569385.61655493</v>
       </c>
       <c r="X3" t="n">
-        <v>60879717.86108911</v>
+        <v>60879718.14731643</v>
       </c>
       <c r="Y3" t="n">
-        <v>1204886443.585938</v>
+        <v>1204886444.666666</v>
       </c>
       <c r="Z3" t="n">
-        <v>1265766161.447026</v>
+        <v>1265766162.813983</v>
       </c>
       <c r="AA3" t="n">
-        <v>7147642996.442022</v>
+        <v>7147642997.808978</v>
       </c>
       <c r="AB3" t="n">
         <v>4383150</v>
@@ -2061,190 +2061,190 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>14892693.39476776</v>
+        <v>14892693.68263883</v>
       </c>
       <c r="AT3" t="n">
-        <v>14892693.39476776</v>
+        <v>14892693.68263883</v>
       </c>
       <c r="AU3" t="n">
-        <v>14892693.39476776</v>
+        <v>14892693.68263883</v>
       </c>
       <c r="AV3" t="n">
-        <v>4061643.653118479</v>
+        <v>4061643.731628773</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.397018787829493e-09</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>4061643.65311848</v>
+        <v>4061643.731628772</v>
       </c>
       <c r="AY3" t="n">
-        <v>4061643.65311848</v>
+        <v>4061643.731628772</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4061643.65311848</v>
+        <v>4061643.731628772</v>
       </c>
       <c r="BA3" t="n">
-        <v>20063960.51446922</v>
+        <v>20063960.52529245</v>
       </c>
       <c r="BB3" t="n">
-        <v>5015270.263554191</v>
+        <v>5015270.252957882</v>
       </c>
       <c r="BC3" t="n">
-        <v>16943082.70513153</v>
+        <v>16943082.50874928</v>
       </c>
       <c r="BD3" t="n">
-        <v>57827555.24576567</v>
+        <v>57827554.54608272</v>
       </c>
       <c r="BE3" t="n">
-        <v>6113901.504415085</v>
+        <v>6113901.504033455</v>
       </c>
       <c r="BF3" t="n">
-        <v>5471989.231218877</v>
+        <v>5471989.234170668</v>
       </c>
       <c r="BG3" t="n">
-        <v>1367800.980969325</v>
+        <v>1367800.978079422</v>
       </c>
       <c r="BH3" t="n">
-        <v>4620840.737763144</v>
+        <v>4620840.684204347</v>
       </c>
       <c r="BI3" t="n">
-        <v>15771151.43066336</v>
+        <v>15771151.23984074</v>
       </c>
       <c r="BJ3" t="n">
-        <v>29238258.61644756</v>
+        <v>29238258.61721074</v>
       </c>
       <c r="BK3" t="n">
-        <v>2969445.110253906</v>
+        <v>2969445.080524007</v>
       </c>
       <c r="BL3" t="n">
-        <v>14580500.91179657</v>
+        <v>14580500.81473149</v>
       </c>
       <c r="BM3" t="n">
-        <v>73702680.33497767</v>
+        <v>73702679.15977043</v>
       </c>
       <c r="BN3" t="n">
-        <v>6428014.2591271</v>
+        <v>6428014.259060434</v>
       </c>
       <c r="BO3" t="n">
-        <v>7974070.531758423</v>
+        <v>7974070.531966563</v>
       </c>
       <c r="BP3" t="n">
-        <v>809848.6664328835</v>
+        <v>809848.6583247292</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3976500.248671792</v>
+        <v>3976500.222199498</v>
       </c>
       <c r="BR3" t="n">
-        <v>20100731.00044846</v>
+        <v>20100730.67993739</v>
       </c>
       <c r="BS3" t="n">
-        <v>35426338.7554962</v>
+        <v>35426338.75963952</v>
       </c>
       <c r="BT3" t="n">
-        <v>28295975.55950069</v>
+        <v>28295975.68698772</v>
       </c>
       <c r="BU3" t="n">
-        <v>51580588.56184959</v>
+        <v>51580588.79418679</v>
       </c>
       <c r="BV3" t="n">
-        <v>122955261.8984108</v>
+        <v>122955261.4885772</v>
       </c>
       <c r="BW3" t="n">
-        <v>16603559.41666067</v>
+        <v>16603559.49472266</v>
       </c>
       <c r="BX3" t="n">
-        <v>9661728.751498962</v>
+        <v>9661728.752628958</v>
       </c>
       <c r="BY3" t="n">
-        <v>7717084.243500189</v>
+        <v>7717084.278269378</v>
       </c>
       <c r="BZ3" t="n">
-        <v>14067433.2441408</v>
+        <v>14067433.30750549</v>
       </c>
       <c r="CA3" t="n">
-        <v>33533253.24502112</v>
+        <v>33533253.13324833</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>1204886443.585938</v>
+        <v>1204886444.666667</v>
       </c>
       <c r="CD3" t="n">
-        <v>1204886443.585938</v>
+        <v>1204886444.666667</v>
       </c>
       <c r="CE3" t="n">
-        <v>1204886443.585938</v>
+        <v>1204886444.666667</v>
       </c>
       <c r="CF3" t="n">
-        <v>328605393.7052556</v>
+        <v>328605393.9999999</v>
       </c>
       <c r="CG3" t="n">
-        <v>5.960613494739169e-08</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>328605393.7052557</v>
+        <v>328605393.9999999</v>
       </c>
       <c r="CI3" t="n">
-        <v>328605393.7052557</v>
+        <v>328605393.9999999</v>
       </c>
       <c r="CJ3" t="n">
-        <v>328605393.7052557</v>
+        <v>328605393.9999999</v>
       </c>
       <c r="CK3" t="n">
-        <v>35426338.7554962</v>
+        <v>35426338.75963952</v>
       </c>
       <c r="CL3" t="n">
-        <v>1233182419.145438</v>
+        <v>1233182420.353654</v>
       </c>
       <c r="CM3" t="n">
-        <v>1256467032.147787</v>
+        <v>1256467033.460853</v>
       </c>
       <c r="CN3" t="n">
-        <v>1327841705.484348</v>
+        <v>1327841706.155244</v>
       </c>
       <c r="CO3" t="n">
-        <v>345208953.1219163</v>
+        <v>345208953.4947226</v>
       </c>
       <c r="CP3" t="n">
-        <v>9661728.751498962</v>
+        <v>9661728.75262896</v>
       </c>
       <c r="CQ3" t="n">
-        <v>336322477.9487559</v>
+        <v>336322478.2782693</v>
       </c>
       <c r="CR3" t="n">
-        <v>342672826.9493964</v>
+        <v>342672827.3075054</v>
       </c>
       <c r="CS3" t="n">
-        <v>362138646.9502768</v>
+        <v>362138647.1332483</v>
       </c>
       <c r="CT3" t="n">
-        <v>35426338.7554962</v>
+        <v>35426338.75963952</v>
       </c>
       <c r="CU3" t="n">
-        <v>7115059254.140433</v>
+        <v>7115059255.348649</v>
       </c>
       <c r="CV3" t="n">
-        <v>7138343867.142782</v>
+        <v>7138343868.455849</v>
       </c>
       <c r="CW3" t="n">
-        <v>7209718540.479343</v>
+        <v>7209718541.150239</v>
       </c>
       <c r="CX3" t="n">
-        <v>1949357180.847824</v>
+        <v>1949357181.22063</v>
       </c>
       <c r="CY3" t="n">
-        <v>9661728.751498964</v>
+        <v>9661728.752628962</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1940470705.674664</v>
+        <v>1940470706.004177</v>
       </c>
       <c r="DA3" t="n">
-        <v>1946821054.675304</v>
+        <v>1946821055.033413</v>
       </c>
       <c r="DB3" t="n">
-        <v>1966286874.676184</v>
+        <v>1966286874.859156</v>
       </c>
       <c r="DC3" t="n">
         <v>3291338827688.013</v>
@@ -2280,91 +2280,91 @@
         <v>0.1986126561485634</v>
       </c>
       <c r="DN3" t="n">
-        <v>708236589697.2211</v>
+        <v>708236584105.7397</v>
       </c>
       <c r="DO3" t="n">
-        <v>340615003425.9276</v>
+        <v>340615001020.1302</v>
       </c>
       <c r="DP3" t="n">
-        <v>278534983062.464</v>
+        <v>278534983883.8187</v>
       </c>
       <c r="DQ3" t="n">
-        <v>642300887024.5479</v>
+        <v>642300888180.8724</v>
       </c>
       <c r="DR3" t="n">
-        <v>1289769928135.821</v>
+        <v>1289769914248.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>708.1679908802805</v>
+        <v>708.1679852893408</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.023539679113522</v>
+        <v>0.02353967892767778</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.01132103028639808</v>
+        <v>0.01132103020643653</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.009257674933151529</v>
+        <v>0.009257674960450917</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.02134817234076</v>
+        <v>0.02134817237919279</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.04286811876179276</v>
+        <v>0.04286811830022778</v>
       </c>
       <c r="DY3" t="n">
-        <v>3999575417385.234</v>
+        <v>3999575411793.753</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1919895196820.816</v>
+        <v>1919895194418.051</v>
       </c>
       <c r="EA3" t="n">
-        <v>1563565297406.276</v>
+        <v>1563565298950.34</v>
       </c>
       <c r="EB3" t="n">
-        <v>3624171409038.832</v>
+        <v>3624171393606.327</v>
       </c>
       <c r="EC3" t="n">
-        <v>7255846079866.871</v>
+        <v>7255846054151.549</v>
       </c>
       <c r="ED3" t="n">
-        <v>3999.188024039722</v>
+        <v>3999.188018448782</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1329339987303238</v>
+        <v>0.1329339985444796</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.06381160973916214</v>
+        <v>0.06381160965930137</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.05196826302029555</v>
+        <v>0.05196826307161564</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.1204566853255163</v>
+        <v>0.1204566848125858</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2411627567705753</v>
+        <v>0.2411627559158744</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.8229312326262481</v>
+        <v>0.8229312337789142</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.00400498981503759</v>
+        <v>0.004004989805799421</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.815826138901906</v>
+        <v>0.8158261386924335</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.8239833965837879</v>
+        <v>0.8239834001856532</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.8266799532049129</v>
+        <v>0.8266799544096675</v>
       </c>
       <c r="EO3" t="n">
         <v>0.8308825156847426</v>
       </c>
       <c r="EP3" t="n">
-        <v>2.220501562483299e-16</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0.8308825156847428</v>
@@ -2376,25 +2376,25 @@
         <v>0.8308825156847428</v>
       </c>
       <c r="ET3" t="n">
-        <v>1.009686493053749</v>
+        <v>1.009686493246847</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.005004376373802738</v>
+        <v>0.005004376374388031</v>
       </c>
       <c r="EV3" t="n">
-        <v>1.005083666008325</v>
+        <v>1.005083666178999</v>
       </c>
       <c r="EW3" t="n">
-        <v>1.008372884462039</v>
+        <v>1.008372884647524</v>
       </c>
       <c r="EX3" t="n">
-        <v>1.018455375102649</v>
+        <v>1.018455375197421</v>
       </c>
       <c r="EY3" t="n">
         <v>0.8308825156847426</v>
       </c>
       <c r="EZ3" t="n">
-        <v>1.009686493053749</v>
+        <v>1.009686493246847</v>
       </c>
       <c r="FA3" t="n">
         <v>0.2604087941745171</v>
@@ -2559,25 +2559,25 @@
         <v>2659873520.816406</v>
       </c>
       <c r="U4" t="n">
-        <v>3571597.590820312</v>
+        <v>3571597.680347249</v>
       </c>
       <c r="V4" t="n">
-        <v>73330206.0548595</v>
+        <v>73330206.07028843</v>
       </c>
       <c r="W4" t="n">
-        <v>41616241.95688199</v>
+        <v>41616241.94342488</v>
       </c>
       <c r="X4" t="n">
-        <v>118518045.6025618</v>
+        <v>118518045.6940606</v>
       </c>
       <c r="Y4" t="n">
-        <v>562978584.5078105</v>
+        <v>562978588.6263</v>
       </c>
       <c r="Z4" t="n">
-        <v>681496630.1103722</v>
+        <v>681496634.3203605</v>
       </c>
       <c r="AA4" t="n">
-        <v>3341370150.926778</v>
+        <v>3341370155.136766</v>
       </c>
       <c r="AB4" t="n">
         <v>1136100</v>
@@ -2631,190 +2631,190 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>3571597.590820312</v>
+        <v>3571597.680347251</v>
       </c>
       <c r="AT4" t="n">
-        <v>3571597.590820312</v>
+        <v>3571597.680347251</v>
       </c>
       <c r="AU4" t="n">
-        <v>3571597.590820312</v>
+        <v>3571597.680347251</v>
       </c>
       <c r="AV4" t="n">
-        <v>974072.0702237213</v>
+        <v>974072.0946401596</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.328364646382488e-10</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>974072.0702237216</v>
+        <v>974072.0946401593</v>
       </c>
       <c r="AY4" t="n">
-        <v>974072.0702237216</v>
+        <v>974072.0946401593</v>
       </c>
       <c r="AZ4" t="n">
-        <v>974072.0702237216</v>
+        <v>974072.0946401593</v>
       </c>
       <c r="BA4" t="n">
-        <v>65631102.75941639</v>
+        <v>65631102.80586216</v>
       </c>
       <c r="BB4" t="n">
-        <v>16405420.95704365</v>
+        <v>16405420.91159559</v>
       </c>
       <c r="BC4" t="n">
-        <v>55422416.96004486</v>
+        <v>55422417.15329136</v>
       </c>
       <c r="BD4" t="n">
-        <v>189159369.421585</v>
+        <v>189159372.2306847</v>
       </c>
       <c r="BE4" t="n">
-        <v>19999147.10587077</v>
+        <v>19999147.11007867</v>
       </c>
       <c r="BF4" t="n">
-        <v>17899391.66165902</v>
+        <v>17899391.67432604</v>
       </c>
       <c r="BG4" t="n">
-        <v>4474205.715557358</v>
+        <v>4474205.703162433</v>
       </c>
       <c r="BH4" t="n">
-        <v>15115204.62546678</v>
+        <v>15115204.67817037</v>
       </c>
       <c r="BI4" t="n">
-        <v>51588918.93315955</v>
+        <v>51588919.69927763</v>
       </c>
       <c r="BJ4" t="n">
-        <v>51625717.55693599</v>
+        <v>51625717.54791986</v>
       </c>
       <c r="BK4" t="n">
-        <v>5243121.087999525</v>
+        <v>5243121.17928099</v>
       </c>
       <c r="BL4" t="n">
-        <v>25744652.87409317</v>
+        <v>25744652.80656143</v>
       </c>
       <c r="BM4" t="n">
-        <v>130136128.2188078</v>
+        <v>130136125.6373705</v>
       </c>
       <c r="BN4" t="n">
-        <v>11349884.17005872</v>
+        <v>11349884.1663886</v>
       </c>
       <c r="BO4" t="n">
-        <v>14079741.15189163</v>
+        <v>14079741.14943269</v>
       </c>
       <c r="BP4" t="n">
-        <v>1429942.114908961</v>
+        <v>1429942.139803906</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7021268.965661774</v>
+        <v>7021268.947244026</v>
       </c>
       <c r="BR4" t="n">
-        <v>35491671.33240213</v>
+        <v>35491670.62837376</v>
       </c>
       <c r="BS4" t="n">
-        <v>83418946.5980861</v>
+        <v>83418946.62795307</v>
       </c>
       <c r="BT4" t="n">
-        <v>38092053.33461795</v>
+        <v>38092053.18776567</v>
       </c>
       <c r="BU4" t="n">
-        <v>97405639.44528821</v>
+        <v>97405639.20418808</v>
       </c>
       <c r="BV4" t="n">
-        <v>269905718.5846128</v>
+        <v>269905715.1168637</v>
       </c>
       <c r="BW4" t="n">
-        <v>32323103.34615322</v>
+        <v>32323103.37110743</v>
       </c>
       <c r="BX4" t="n">
-        <v>22750621.79947802</v>
+        <v>22750621.80762357</v>
       </c>
       <c r="BY4" t="n">
-        <v>10388741.81853217</v>
+        <v>10388741.77848154</v>
       </c>
       <c r="BZ4" t="n">
-        <v>26565174.39416951</v>
+        <v>26565174.32841492</v>
       </c>
       <c r="CA4" t="n">
-        <v>73610650.52307621</v>
+        <v>73610649.57732645</v>
       </c>
       <c r="CB4" t="n">
-        <v>1.192122698947834e-07</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>562978584.5078104</v>
+        <v>562978588.6263</v>
       </c>
       <c r="CD4" t="n">
-        <v>562978584.5078104</v>
+        <v>562978588.6263</v>
       </c>
       <c r="CE4" t="n">
-        <v>562978584.5078104</v>
+        <v>562978588.6263</v>
       </c>
       <c r="CF4" t="n">
-        <v>153539613.9566755</v>
+        <v>153539615.0799</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>153539613.9566755</v>
+        <v>153539615.0799</v>
       </c>
       <c r="CI4" t="n">
-        <v>153539613.9566755</v>
+        <v>153539615.0799</v>
       </c>
       <c r="CJ4" t="n">
-        <v>153539613.9566755</v>
+        <v>153539615.0799</v>
       </c>
       <c r="CK4" t="n">
-        <v>83418946.5980861</v>
+        <v>83418946.62795307</v>
       </c>
       <c r="CL4" t="n">
-        <v>601070637.8424283</v>
+        <v>601070641.8140657</v>
       </c>
       <c r="CM4" t="n">
-        <v>660384223.9530985</v>
+        <v>660384227.8304881</v>
       </c>
       <c r="CN4" t="n">
-        <v>832884303.0924231</v>
+        <v>832884303.7431637</v>
       </c>
       <c r="CO4" t="n">
-        <v>185862717.3028287</v>
+        <v>185862718.4510074</v>
       </c>
       <c r="CP4" t="n">
-        <v>22750621.79947802</v>
+        <v>22750621.80762356</v>
       </c>
       <c r="CQ4" t="n">
-        <v>163928355.7752077</v>
+        <v>163928356.8583815</v>
       </c>
       <c r="CR4" t="n">
-        <v>180104788.350845</v>
+        <v>180104789.4083149</v>
       </c>
       <c r="CS4" t="n">
-        <v>227150264.4797517</v>
+        <v>227150264.6572264</v>
       </c>
       <c r="CT4" t="n">
-        <v>83418946.59808613</v>
+        <v>83418946.62795307</v>
       </c>
       <c r="CU4" t="n">
-        <v>3260944158.658835</v>
+        <v>3260944162.630472</v>
       </c>
       <c r="CV4" t="n">
-        <v>3320257744.769505</v>
+        <v>3320257748.646894</v>
       </c>
       <c r="CW4" t="n">
-        <v>3492757823.90883</v>
+        <v>3492757824.55957</v>
       </c>
       <c r="CX4" t="n">
-        <v>911282768.4345758</v>
+        <v>911282769.5827545</v>
       </c>
       <c r="CY4" t="n">
-        <v>22750621.79947804</v>
+        <v>22750621.80762356</v>
       </c>
       <c r="CZ4" t="n">
-        <v>889348406.9069549</v>
+        <v>889348407.9901285</v>
       </c>
       <c r="DA4" t="n">
-        <v>905524839.4825921</v>
+        <v>905524840.5400621</v>
       </c>
       <c r="DB4" t="n">
-        <v>952570315.611499</v>
+        <v>952570315.7889736</v>
       </c>
       <c r="DC4" t="n">
         <v>1488393115214.424</v>
@@ -2850,91 +2850,91 @@
         <v>0.071151376578477</v>
       </c>
       <c r="DN4" t="n">
-        <v>381276295256.5449</v>
+        <v>381276297662.0823</v>
       </c>
       <c r="DO4" t="n">
-        <v>190059077998.3028</v>
+        <v>190059078986.9814</v>
       </c>
       <c r="DP4" t="n">
-        <v>147797623267.0039</v>
+        <v>147797624707.0695</v>
       </c>
       <c r="DQ4" t="n">
-        <v>344850593859.0859</v>
+        <v>344850601339.4841</v>
       </c>
       <c r="DR4" t="n">
-        <v>719712143206.9435</v>
+        <v>719712140229.7621</v>
       </c>
       <c r="DS4" t="n">
-        <v>80.03288333435113</v>
+        <v>80.03288383929227</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.01003906576374827</v>
+        <v>0.01003906582708646</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.005004285886009516</v>
+        <v>0.00500428591204158</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.003891535031583305</v>
+        <v>0.003891535069500462</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.009079971226875223</v>
+        <v>0.009079971423835303</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01895013570607939</v>
+        <v>0.01895013562768973</v>
       </c>
       <c r="DY4" t="n">
-        <v>1869669410470.969</v>
+        <v>1869669412876.506</v>
       </c>
       <c r="DZ4" t="n">
-        <v>898980099624.1754</v>
+        <v>898980100665.3237</v>
       </c>
       <c r="EA4" t="n">
-        <v>736611016334.933</v>
+        <v>736611018099.7356</v>
       </c>
       <c r="EB4" t="n">
-        <v>1696252744427.25</v>
+        <v>1696252739653.217</v>
       </c>
       <c r="EC4" t="n">
-        <v>3399216764920.097</v>
+        <v>3399216769608.655</v>
       </c>
       <c r="ED4" t="n">
-        <v>392.4582662589734</v>
+        <v>392.4582667639145</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.04922869426109259</v>
+        <v>0.04922869432443076</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.02367028963695626</v>
+        <v>0.02367028966436986</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.01939508573516781</v>
+        <v>0.01939508578163535</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.04466260574050555</v>
+        <v>0.04466260561480451</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.08950192045195791</v>
+        <v>0.0895019205754084</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.7965021755023067</v>
+        <v>0.7965021744703221</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01849532125918064</v>
+        <v>0.018495321202631</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.7615396405002186</v>
+        <v>0.7615396382339884</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.8011045277762315</v>
+        <v>0.8011045293274488</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.8156758867533375</v>
+        <v>0.8156758846970822</v>
       </c>
       <c r="EO4" t="n">
         <v>0.1151307801577142</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.775626953104124e-17</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="n">
         <v>0.1151307801577141</v>
@@ -2946,25 +2946,25 @@
         <v>0.1151307801577141</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1446288890284615</v>
+        <v>0.1446288892106879</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.003610731234628226</v>
+        <v>0.003610731235920996</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.1411477057457599</v>
+        <v>0.1411477059176694</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.1437150531739102</v>
+        <v>0.1437150533417403</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.1511815994337798</v>
+        <v>0.1511815994619466</v>
       </c>
       <c r="EY4" t="n">
         <v>0.1151307801577142</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.1446288890284615</v>
+        <v>0.1446288892106879</v>
       </c>
       <c r="FA4" t="n">
         <v>0.1773882185018733</v>
@@ -3121,25 +3121,25 @@
         <v>29584895.36180115</v>
       </c>
       <c r="U5" t="n">
-        <v>36776.82800292969</v>
+        <v>36776.82940038799</v>
       </c>
       <c r="V5" t="n">
-        <v>79945099.52353095</v>
+        <v>79945099.5314104</v>
       </c>
       <c r="W5" t="n">
-        <v>3586027.290856226</v>
+        <v>3586027.290965894</v>
       </c>
       <c r="X5" t="n">
-        <v>83567903.6423901</v>
+        <v>83567903.6517767</v>
       </c>
       <c r="Y5" t="n">
-        <v>22288610.8203125</v>
+        <v>22288610.66666666</v>
       </c>
       <c r="Z5" t="n">
-        <v>105856514.4627026</v>
+        <v>105856514.3184434</v>
       </c>
       <c r="AA5" t="n">
-        <v>135441409.8245037</v>
+        <v>135441409.6802445</v>
       </c>
       <c r="AB5" t="n">
         <v>30600</v>
@@ -3185,190 +3185,190 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>36776.82800292969</v>
+        <v>36776.82940038799</v>
       </c>
       <c r="AT5" t="n">
-        <v>36776.82800292969</v>
+        <v>36776.82940038799</v>
       </c>
       <c r="AU5" t="n">
-        <v>36776.82800292969</v>
+        <v>36776.82940038799</v>
       </c>
       <c r="AV5" t="n">
-        <v>10030.04400079901</v>
+        <v>10030.044381924</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.819034879986319e-12</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>10030.04400079901</v>
+        <v>10030.044381924</v>
       </c>
       <c r="AY5" t="n">
-        <v>10030.04400079901</v>
+        <v>10030.044381924</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10030.04400079901</v>
+        <v>10030.044381924</v>
       </c>
       <c r="BA5" t="n">
-        <v>71551483.6859134</v>
+        <v>71551483.72475098</v>
       </c>
       <c r="BB5" t="n">
-        <v>17885303.31800079</v>
+        <v>17885303.7229305</v>
       </c>
       <c r="BC5" t="n">
-        <v>60421903.99703979</v>
+        <v>60421903.78333674</v>
       </c>
       <c r="BD5" t="n">
-        <v>206222856.9857543</v>
+        <v>206222860.2737882</v>
       </c>
       <c r="BE5" t="n">
-        <v>21803208.96096298</v>
+        <v>21803208.96311193</v>
       </c>
       <c r="BF5" t="n">
-        <v>19514041.00524911</v>
+        <v>19514041.01584117</v>
       </c>
       <c r="BG5" t="n">
-        <v>4877809.995818398</v>
+        <v>4877810.106253772</v>
       </c>
       <c r="BH5" t="n">
-        <v>16478701.09010176</v>
+        <v>16478701.03181911</v>
       </c>
       <c r="BI5" t="n">
-        <v>56242597.35975118</v>
+        <v>56242598.25648769</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4448533.149101539</v>
+        <v>4448533.154296194</v>
       </c>
       <c r="BK5" t="n">
-        <v>451794.1836261034</v>
+        <v>451794.1736378605</v>
       </c>
       <c r="BL5" t="n">
-        <v>2218389.363997459</v>
+        <v>2218389.341504613</v>
       </c>
       <c r="BM5" t="n">
-        <v>11213691.40255279</v>
+        <v>11213691.48878442</v>
       </c>
       <c r="BN5" t="n">
-        <v>978007.4429607891</v>
+        <v>978007.4429906983</v>
       </c>
       <c r="BO5" t="n">
-        <v>1213236.313391329</v>
+        <v>1213236.314808053</v>
       </c>
       <c r="BP5" t="n">
-        <v>123216.5955343918</v>
+        <v>123216.5928103256</v>
       </c>
       <c r="BQ5" t="n">
-        <v>605015.2810902162</v>
+        <v>605015.2749558035</v>
       </c>
       <c r="BR5" t="n">
-        <v>3058279.473423488</v>
+        <v>3058279.496941206</v>
       </c>
       <c r="BS5" t="n">
-        <v>71680507.22876458</v>
+        <v>71680507.26824862</v>
       </c>
       <c r="BT5" t="n">
-        <v>20841847.87571084</v>
+        <v>20841848.23103109</v>
       </c>
       <c r="BU5" t="n">
-        <v>64356294.99843502</v>
+        <v>64356294.78784442</v>
       </c>
       <c r="BV5" t="n">
-        <v>210006114.9938577</v>
+        <v>210006119.4372151</v>
       </c>
       <c r="BW5" t="n">
-        <v>22791246.44792457</v>
+        <v>22791246.45048455</v>
       </c>
       <c r="BX5" t="n">
-        <v>19549229.24420852</v>
+        <v>19549229.25497689</v>
       </c>
       <c r="BY5" t="n">
-        <v>5684140.329739321</v>
+        <v>5684140.426644844</v>
       </c>
       <c r="BZ5" t="n">
-        <v>17551716.81775501</v>
+        <v>17551716.7603212</v>
       </c>
       <c r="CA5" t="n">
-        <v>57274394.99832482</v>
+        <v>57274396.21014956</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>22288610.8203125</v>
+        <v>22288610.66666666</v>
       </c>
       <c r="CD5" t="n">
-        <v>22288610.8203125</v>
+        <v>22288610.66666666</v>
       </c>
       <c r="CE5" t="n">
-        <v>22288610.8203125</v>
+        <v>22288610.66666666</v>
       </c>
       <c r="CF5" t="n">
-        <v>6078712.041903407</v>
+        <v>6078711.999999999</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.313458585529952e-10</v>
+        <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>6078712.041903408</v>
+        <v>6078711.999999999</v>
       </c>
       <c r="CI5" t="n">
-        <v>6078712.041903408</v>
+        <v>6078711.999999999</v>
       </c>
       <c r="CJ5" t="n">
-        <v>6078712.041903408</v>
+        <v>6078711.999999999</v>
       </c>
       <c r="CK5" t="n">
-        <v>71680507.22876458</v>
+        <v>71680507.26824862</v>
       </c>
       <c r="CL5" t="n">
-        <v>43130458.69602334</v>
+        <v>43130458.89769776</v>
       </c>
       <c r="CM5" t="n">
-        <v>86644905.81874752</v>
+        <v>86644905.45451108</v>
       </c>
       <c r="CN5" t="n">
-        <v>232294725.8141702</v>
+        <v>232294730.1038817</v>
       </c>
       <c r="CO5" t="n">
-        <v>28869958.48982798</v>
+        <v>28869958.45048454</v>
       </c>
       <c r="CP5" t="n">
-        <v>19549229.24420853</v>
+        <v>19549229.25497689</v>
       </c>
       <c r="CQ5" t="n">
-        <v>11762852.37164273</v>
+        <v>11762852.42664484</v>
       </c>
       <c r="CR5" t="n">
-        <v>23630428.85965841</v>
+        <v>23630428.7603212</v>
       </c>
       <c r="CS5" t="n">
-        <v>63353107.04022823</v>
+        <v>63353108.21014955</v>
       </c>
       <c r="CT5" t="n">
-        <v>71680507.22876458</v>
+        <v>71680507.26824862</v>
       </c>
       <c r="CU5" t="n">
-        <v>72715354.05782449</v>
+        <v>72715354.25949891</v>
       </c>
       <c r="CV5" t="n">
-        <v>116229801.1805487</v>
+        <v>116229800.8163122</v>
       </c>
       <c r="CW5" t="n">
-        <v>261879621.1759713</v>
+        <v>261879625.4656829</v>
       </c>
       <c r="CX5" t="n">
-        <v>36938566.31577375</v>
+        <v>36938566.27643031</v>
       </c>
       <c r="CY5" t="n">
-        <v>19549229.24420853</v>
+        <v>19549229.25497689</v>
       </c>
       <c r="CZ5" t="n">
-        <v>19831460.1975885</v>
+        <v>19831460.25259061</v>
       </c>
       <c r="DA5" t="n">
-        <v>31699036.68560418</v>
+        <v>31699036.58626696</v>
       </c>
       <c r="DB5" t="n">
-        <v>71421714.866174</v>
+        <v>71421716.03609532</v>
       </c>
       <c r="DC5" t="n">
         <v>16554905439.73613</v>
@@ -3404,91 +3404,91 @@
         <v>0.07772339599576007</v>
       </c>
       <c r="DN5" t="n">
-        <v>59273722724.83598</v>
+        <v>59273722484.09464</v>
       </c>
       <c r="DO5" t="n">
-        <v>52413212676.66793</v>
+        <v>52413212260.31626</v>
       </c>
       <c r="DP5" t="n">
-        <v>15580502482.57812</v>
+        <v>15580502659.82487</v>
       </c>
       <c r="DQ5" t="n">
-        <v>45109457652.19727</v>
+        <v>45109459142.1362</v>
       </c>
       <c r="DR5" t="n">
-        <v>149151491919.3326</v>
+        <v>149151481910.9467</v>
       </c>
       <c r="DS5" t="n">
-        <v>1363.355730298665</v>
+        <v>1363.35572476137</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1532763417866129</v>
+        <v>0.1532763411640782</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.1355356999872935</v>
+        <v>0.1355356989106467</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.04028973234586768</v>
+        <v>0.0402897328042113</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1166488678466258</v>
+        <v>0.1166488716994695</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.3856919053243779</v>
+        <v>0.3856918794436216</v>
       </c>
       <c r="DY5" t="n">
-        <v>75828628164.5721</v>
+        <v>75828627923.83078</v>
       </c>
       <c r="DZ5" t="n">
-        <v>57157913897.93362</v>
+        <v>57157913489.70263</v>
       </c>
       <c r="EA5" t="n">
-        <v>23646010710.43906</v>
+        <v>23646010165.91803</v>
       </c>
       <c r="EB5" t="n">
-        <v>60934338194.90234</v>
+        <v>60934337964.53952</v>
       </c>
       <c r="EC5" t="n">
-        <v>174462582242.9547</v>
+        <v>174462574272.3645</v>
       </c>
       <c r="ED5" t="n">
-        <v>1744.13534322417</v>
+        <v>1744.135337686876</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.1960857896798332</v>
+        <v>0.1960857890572985</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.1478050566707291</v>
+        <v>0.1478050556150817</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.06114638752096699</v>
+        <v>0.06114638611288616</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.1575705391588218</v>
+        <v>0.157570538563125</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.4511440340770361</v>
+        <v>0.4511440134658303</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2565409439648406</v>
+        <v>0.2565409444509626</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.08906975943490619</v>
+        <v>0.08906975952357722</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.1129713505076369</v>
+        <v>0.1129713525546581</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2545379482612794</v>
+        <v>0.2545379470136681</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.4068590034762058</v>
+        <v>0.4068589878340525</v>
       </c>
       <c r="EO5" t="n">
         <v>0.2571576794882419</v>
       </c>
       <c r="EP5" t="n">
-        <v>5.551253906208248e-17</v>
+        <v>0</v>
       </c>
       <c r="EQ5" t="n">
         <v>0.2571576794882419</v>
@@ -3500,25 +3500,25 @@
         <v>0.2571576794882419</v>
       </c>
       <c r="ET5" t="n">
-        <v>1.17728314503543</v>
+        <v>1.1772831437815</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.6230609464074516</v>
+        <v>0.6230609467506545</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.6320560368389836</v>
+        <v>0.6320560385919769</v>
       </c>
       <c r="EW5" t="n">
-        <v>1.010292096471688</v>
+        <v>1.010292093305674</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.276308733335086</v>
+        <v>2.276308770622095</v>
       </c>
       <c r="EY5" t="n">
         <v>0.2571576794882419</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1.17728314503543</v>
+        <v>1.1772831437815</v>
       </c>
       <c r="FA5" t="n">
         <v>0.3543684121672946</v>
@@ -3679,25 +3679,25 @@
         <v>3051209365.508163</v>
       </c>
       <c r="U6" t="n">
-        <v>6784318.533340454</v>
+        <v>6784318.480330408</v>
       </c>
       <c r="V6" t="n">
-        <v>13922314.97171663</v>
+        <v>13922314.974172</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>20706633.50505708</v>
+        <v>20706633.4545024</v>
       </c>
       <c r="Y6" t="n">
-        <v>713331654.0208321</v>
+        <v>713331655.6666663</v>
       </c>
       <c r="Z6" t="n">
-        <v>734038287.5258892</v>
+        <v>734038289.121169</v>
       </c>
       <c r="AA6" t="n">
-        <v>3785247653.034052</v>
+        <v>3785247654.629332</v>
       </c>
       <c r="AB6" t="n">
         <v>95100</v>
@@ -3743,55 +3743,55 @@
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>6784318.533340454</v>
+        <v>6784318.480330408</v>
       </c>
       <c r="AT6" t="n">
-        <v>6784318.533340454</v>
+        <v>6784318.480330408</v>
       </c>
       <c r="AU6" t="n">
-        <v>6784318.533340454</v>
+        <v>6784318.480330408</v>
       </c>
       <c r="AV6" t="n">
-        <v>1850268.690911032</v>
+        <v>1850268.676453747</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.328364646382488e-10</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1850268.690911033</v>
+        <v>1850268.676453747</v>
       </c>
       <c r="AY6" t="n">
-        <v>1850268.690911033</v>
+        <v>1850268.676453747</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1850268.690911033</v>
+        <v>1850268.676453747</v>
       </c>
       <c r="BA6" t="n">
-        <v>12460579.79852873</v>
+        <v>12460579.81194873</v>
       </c>
       <c r="BB6" t="n">
-        <v>3114697.932041097</v>
+        <v>3114697.877654597</v>
       </c>
       <c r="BC6" t="n">
-        <v>10522380.79477596</v>
+        <v>10522380.74305251</v>
       </c>
       <c r="BD6" t="n">
-        <v>35913391.22546157</v>
+        <v>35913390.96999044</v>
       </c>
       <c r="BE6" t="n">
-        <v>3796994.992286352</v>
+        <v>3796994.992955999</v>
       </c>
       <c r="BF6" t="n">
-        <v>3398339.94505329</v>
+        <v>3398339.948713291</v>
       </c>
       <c r="BG6" t="n">
-        <v>849463.0723748446</v>
+        <v>849463.0575421627</v>
       </c>
       <c r="BH6" t="n">
-        <v>2869740.216757081</v>
+        <v>2869740.202650684</v>
       </c>
       <c r="BI6" t="n">
-        <v>9794561.243307699</v>
+        <v>9794561.173633756</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3821,112 +3821,112 @@
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>12460579.79852873</v>
+        <v>12460579.81194873</v>
       </c>
       <c r="BT6" t="n">
-        <v>9899016.465381552</v>
+        <v>9899016.357985001</v>
       </c>
       <c r="BU6" t="n">
-        <v>17306699.32811642</v>
+        <v>17306699.22338291</v>
       </c>
       <c r="BV6" t="n">
-        <v>42697709.75880203</v>
+        <v>42697709.45032085</v>
       </c>
       <c r="BW6" t="n">
-        <v>5647263.683197385</v>
+        <v>5647263.669409745</v>
       </c>
       <c r="BX6" t="n">
-        <v>3398339.94505329</v>
+        <v>3398339.94871329</v>
       </c>
       <c r="BY6" t="n">
-        <v>2699731.763285877</v>
+        <v>2699731.733995909</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4720008.907668114</v>
+        <v>4720008.87910443</v>
       </c>
       <c r="CA6" t="n">
-        <v>11644829.93421873</v>
+        <v>11644829.8500875</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>713331654.0208321</v>
+        <v>713331655.6666665</v>
       </c>
       <c r="CD6" t="n">
-        <v>713331654.0208321</v>
+        <v>713331655.6666665</v>
       </c>
       <c r="CE6" t="n">
-        <v>713331654.0208321</v>
+        <v>713331655.6666665</v>
       </c>
       <c r="CF6" t="n">
-        <v>194544996.551136</v>
+        <v>194544997</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>194544996.551136</v>
+        <v>194544996.9999999</v>
       </c>
       <c r="CI6" t="n">
-        <v>194544996.551136</v>
+        <v>194544996.9999999</v>
       </c>
       <c r="CJ6" t="n">
-        <v>194544996.551136</v>
+        <v>194544996.9999999</v>
       </c>
       <c r="CK6" t="n">
-        <v>12460579.79852873</v>
+        <v>12460579.81194873</v>
       </c>
       <c r="CL6" t="n">
-        <v>723230670.4862136</v>
+        <v>723230672.0246515</v>
       </c>
       <c r="CM6" t="n">
-        <v>730638353.3489485</v>
+        <v>730638354.8900495</v>
       </c>
       <c r="CN6" t="n">
-        <v>756029363.7796341</v>
+        <v>756029365.1169873</v>
       </c>
       <c r="CO6" t="n">
-        <v>200192260.2343334</v>
+        <v>200192260.6694097</v>
       </c>
       <c r="CP6" t="n">
-        <v>3398339.945053289</v>
+        <v>3398339.94871329</v>
       </c>
       <c r="CQ6" t="n">
-        <v>197244728.3144219</v>
+        <v>197244728.7339959</v>
       </c>
       <c r="CR6" t="n">
-        <v>199265005.4588041</v>
+        <v>199265005.8791044</v>
       </c>
       <c r="CS6" t="n">
-        <v>206189826.4853547</v>
+        <v>206189826.8500874</v>
       </c>
       <c r="CT6" t="n">
-        <v>12460579.79852873</v>
+        <v>12460579.81194873</v>
       </c>
       <c r="CU6" t="n">
-        <v>3774440035.994377</v>
+        <v>3774440037.532815</v>
       </c>
       <c r="CV6" t="n">
-        <v>3781847718.857112</v>
+        <v>3781847720.398213</v>
       </c>
       <c r="CW6" t="n">
-        <v>3807238729.287797</v>
+        <v>3807238730.625151</v>
       </c>
       <c r="CX6" t="n">
-        <v>1032340269.009287</v>
+        <v>1032340269.444363</v>
       </c>
       <c r="CY6" t="n">
-        <v>3398339.94505329</v>
+        <v>3398339.948713291</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1029392737.089375</v>
+        <v>1029392737.508949</v>
       </c>
       <c r="DA6" t="n">
-        <v>1031413014.233758</v>
+        <v>1031413014.654058</v>
       </c>
       <c r="DB6" t="n">
-        <v>1038337835.260308</v>
+        <v>1038337835.625041</v>
       </c>
       <c r="DC6" t="n">
         <v>1707374047560.901</v>
@@ -3962,91 +3962,91 @@
         <v>0.1394301062295875</v>
       </c>
       <c r="DN6" t="n">
-        <v>410756508345.4541</v>
+        <v>410756509291.0859</v>
       </c>
       <c r="DO6" t="n">
-        <v>197362453091.0426</v>
+        <v>197362453625.2659</v>
       </c>
       <c r="DP6" t="n">
-        <v>161381883368.9808</v>
+        <v>161381888081.0161</v>
       </c>
       <c r="DQ6" t="n">
-        <v>372361149699.5068</v>
+        <v>372361152689.0201</v>
       </c>
       <c r="DR6" t="n">
-        <v>746386133706.0819</v>
+        <v>746386123072.8698</v>
       </c>
       <c r="DS6" t="n">
-        <v>554.2308288254965</v>
+        <v>554.2308301014307</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.01847566979863135</v>
+        <v>0.0184756698411655</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.008877287248949142</v>
+        <v>0.008877287272978302</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.007258895058332003</v>
+        <v>0.00725889527027754</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.01674866133076808</v>
+        <v>0.01674866146523524</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.03357216128887978</v>
+        <v>0.03357216081060199</v>
       </c>
       <c r="DY6" t="n">
-        <v>2118130555906.355</v>
+        <v>2118130556851.986</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1016781887064.716</v>
+        <v>1016781887595.402</v>
       </c>
       <c r="EA6" t="n">
-        <v>827606324284.7234</v>
+        <v>827606322580.1984</v>
       </c>
       <c r="EB6" t="n">
-        <v>1919886698533.81</v>
+        <v>1919886700704.809</v>
       </c>
       <c r="EC6" t="n">
-        <v>3847381837142.633</v>
+        <v>3847381834025.858</v>
       </c>
       <c r="ED6" t="n">
-        <v>2857.978460984697</v>
+        <v>2857.97846226063</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.09527269792741767</v>
+        <v>0.09527269796995183</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.04573445830062857</v>
+        <v>0.04573445832449865</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.03722541422979449</v>
+        <v>0.03722541415312561</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.08635576545280982</v>
+        <v>0.08635576555046054</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.1730537556145472</v>
+        <v>0.1730537554743559</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.8060877822487329</v>
+        <v>0.8060877818947881</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.002610768852634434</v>
+        <v>0.002610768857307523</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.8014231802821721</v>
+        <v>0.8014231804720834</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.8068038654706984</v>
+        <v>0.8068038684775238</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.8083872919843541</v>
+        <v>0.8083872911187081</v>
       </c>
       <c r="EO6" t="n">
         <v>0.6271543750823928</v>
       </c>
       <c r="EP6" t="n">
-        <v>1.11025078124165e-16</v>
+        <v>0</v>
       </c>
       <c r="EQ6" t="n">
         <v>0.6271543750823929</v>
@@ -4058,25 +4058,25 @@
         <v>0.6271543750823929</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.7780307222461933</v>
+        <v>0.7780307225740918</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.002561183517935707</v>
+        <v>0.002561183520694093</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.7758092934621613</v>
+        <v>0.7758092937783764</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.7773318899673716</v>
+        <v>0.7773318902841339</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.7825508314990075</v>
+        <v>0.782550831773891</v>
       </c>
       <c r="EY6" t="n">
         <v>0.6271543750823928</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.7780307222461933</v>
+        <v>0.7780307225740918</v>
       </c>
       <c r="FA6" t="n">
         <v>0.01561558918873048</v>
@@ -4237,25 +4237,25 @@
         <v>834388792.213623</v>
       </c>
       <c r="U7" t="n">
-        <v>8226593.642011999</v>
+        <v>8226593.843250062</v>
       </c>
       <c r="V7" t="n">
-        <v>53008581.8933249</v>
+        <v>53008581.88903525</v>
       </c>
       <c r="W7" t="n">
-        <v>11937725.78864898</v>
+        <v>11937725.79130154</v>
       </c>
       <c r="X7" t="n">
-        <v>73172901.32398589</v>
+        <v>73172901.52358685</v>
       </c>
       <c r="Y7" t="n">
-        <v>648485717.1875</v>
+        <v>648485720.6666667</v>
       </c>
       <c r="Z7" t="n">
-        <v>721658618.5114858</v>
+        <v>721658622.1902537</v>
       </c>
       <c r="AA7" t="n">
-        <v>1556047410.725109</v>
+        <v>1556047414.403877</v>
       </c>
       <c r="AB7" t="n">
         <v>494670</v>
@@ -4306,193 +4306,193 @@
         <v>227560579.6946245</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.313458585529952e-10</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>8226593.642012</v>
+        <v>8226593.843250059</v>
       </c>
       <c r="AT7" t="n">
-        <v>8226593.642012</v>
+        <v>8226593.843250059</v>
       </c>
       <c r="AU7" t="n">
-        <v>8226593.642012</v>
+        <v>8226593.843250059</v>
       </c>
       <c r="AV7" t="n">
-        <v>2243616.447821454</v>
+        <v>2243616.502704561</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.656729292764976e-10</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>2243616.447821455</v>
+        <v>2243616.502704561</v>
       </c>
       <c r="AY7" t="n">
-        <v>2243616.447821455</v>
+        <v>2243616.502704561</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2243616.447821455</v>
+        <v>2243616.502704561</v>
       </c>
       <c r="BA7" t="n">
-        <v>47443091.64152176</v>
+        <v>47443091.65335679</v>
       </c>
       <c r="BB7" t="n">
-        <v>11859070.60097656</v>
+        <v>11859070.69431729</v>
       </c>
       <c r="BC7" t="n">
-        <v>40063487.453125</v>
+        <v>40063486.73481861</v>
       </c>
       <c r="BD7" t="n">
-        <v>136738604.921875</v>
+        <v>136738604.8711987</v>
       </c>
       <c r="BE7" t="n">
-        <v>14456885.97090679</v>
+        <v>14456885.96973688</v>
       </c>
       <c r="BF7" t="n">
-        <v>12939024.9931423</v>
+        <v>12939024.99637003</v>
       </c>
       <c r="BG7" t="n">
-        <v>3234291.982084516</v>
+        <v>3234292.00754108</v>
       </c>
       <c r="BH7" t="n">
-        <v>10926405.66903409</v>
+        <v>10926405.47313235</v>
       </c>
       <c r="BI7" t="n">
-        <v>37292346.79687499</v>
+        <v>37292346.78305418</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14808969.5270009</v>
+        <v>14808969.55337944</v>
       </c>
       <c r="BK7" t="n">
-        <v>1504002.798239014</v>
+        <v>1504002.76444738</v>
       </c>
       <c r="BL7" t="n">
-        <v>7384919.653254867</v>
+        <v>7384919.719920764</v>
       </c>
       <c r="BM7" t="n">
-        <v>37329881.75143506</v>
+        <v>37329881.57636236</v>
       </c>
       <c r="BN7" t="n">
-        <v>3255743.396904266</v>
+        <v>3255743.397627692</v>
       </c>
       <c r="BO7" t="n">
-        <v>4038809.871000246</v>
+        <v>4038809.878194391</v>
       </c>
       <c r="BP7" t="n">
-        <v>410182.5813379128</v>
+        <v>410182.5721220126</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2014068.996342236</v>
+        <v>2014069.014523844</v>
       </c>
       <c r="BR7" t="n">
-        <v>10180876.84130047</v>
+        <v>10180876.79355337</v>
       </c>
       <c r="BS7" t="n">
-        <v>49671549.53782449</v>
+        <v>49671549.55791415</v>
       </c>
       <c r="BT7" t="n">
-        <v>27022279.88735269</v>
+        <v>27022279.92427404</v>
       </c>
       <c r="BU7" t="n">
-        <v>60512077.85838604</v>
+        <v>60512078.42775913</v>
       </c>
       <c r="BV7" t="n">
-        <v>161441748.6999041</v>
+        <v>161441747.5605215</v>
       </c>
       <c r="BW7" t="n">
-        <v>19956245.81563251</v>
+        <v>19956245.87006914</v>
       </c>
       <c r="BX7" t="n">
-        <v>13546786.2375885</v>
+        <v>13546786.24306749</v>
       </c>
       <c r="BY7" t="n">
-        <v>7369712.696550732</v>
+        <v>7369712.706620191</v>
       </c>
       <c r="BZ7" t="n">
-        <v>16503293.96137801</v>
+        <v>16503294.11666158</v>
       </c>
       <c r="CA7" t="n">
-        <v>44029567.82724658</v>
+        <v>44029567.51650587</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>648485717.1875</v>
+        <v>648485720.6666667</v>
       </c>
       <c r="CD7" t="n">
-        <v>648485717.1875</v>
+        <v>648485720.6666667</v>
       </c>
       <c r="CE7" t="n">
-        <v>648485717.1875</v>
+        <v>648485720.6666667</v>
       </c>
       <c r="CF7" t="n">
-        <v>176859741.0511363</v>
+        <v>176859742</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.980306747369585e-08</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>176859741.0511363</v>
+        <v>176859742</v>
       </c>
       <c r="CI7" t="n">
-        <v>176859741.0511363</v>
+        <v>176859742</v>
       </c>
       <c r="CJ7" t="n">
-        <v>176859741.0511363</v>
+        <v>176859742</v>
       </c>
       <c r="CK7" t="n">
-        <v>49671549.53782449</v>
+        <v>49671549.55791415</v>
       </c>
       <c r="CL7" t="n">
-        <v>675507997.0748527</v>
+        <v>675508000.5909407</v>
       </c>
       <c r="CM7" t="n">
-        <v>708997795.045886</v>
+        <v>708997799.0944259</v>
       </c>
       <c r="CN7" t="n">
-        <v>809927465.8874041</v>
+        <v>809927468.2271882</v>
       </c>
       <c r="CO7" t="n">
-        <v>196815986.8667688</v>
+        <v>196815987.8700692</v>
       </c>
       <c r="CP7" t="n">
-        <v>13546786.2375885</v>
+        <v>13546786.24306749</v>
       </c>
       <c r="CQ7" t="n">
-        <v>184229453.7476871</v>
+        <v>184229454.7066202</v>
       </c>
       <c r="CR7" t="n">
-        <v>193363035.0125144</v>
+        <v>193363036.1166616</v>
       </c>
       <c r="CS7" t="n">
-        <v>220889308.8783829</v>
+        <v>220889309.5165058</v>
       </c>
       <c r="CT7" t="n">
-        <v>49671549.5378245</v>
+        <v>49671549.55791415</v>
       </c>
       <c r="CU7" t="n">
-        <v>1509896789.288476</v>
+        <v>1509896792.804564</v>
       </c>
       <c r="CV7" t="n">
-        <v>1543386587.259509</v>
+        <v>1543386591.308049</v>
       </c>
       <c r="CW7" t="n">
-        <v>1644316258.101027</v>
+        <v>1644316260.440811</v>
       </c>
       <c r="CX7" t="n">
-        <v>424376566.5613933</v>
+        <v>424376567.5646936</v>
       </c>
       <c r="CY7" t="n">
-        <v>13546786.2375885</v>
+        <v>13546786.24306749</v>
       </c>
       <c r="CZ7" t="n">
-        <v>411790033.4423115</v>
+        <v>411790034.4012446</v>
       </c>
       <c r="DA7" t="n">
-        <v>420923614.7071388</v>
+        <v>420923615.811286</v>
       </c>
       <c r="DB7" t="n">
-        <v>448449888.5730074</v>
+        <v>448449889.2111303</v>
       </c>
       <c r="DC7" t="n">
         <v>466901348388.299</v>
@@ -4528,91 +4528,91 @@
         <v>0.4364330474112158</v>
       </c>
       <c r="DN7" t="n">
-        <v>403820015833.1622</v>
+        <v>403820016763.6094</v>
       </c>
       <c r="DO7" t="n">
-        <v>196351271781.8308</v>
+        <v>196351272084.6765</v>
       </c>
       <c r="DP7" t="n">
-        <v>157830867709.0879</v>
+        <v>157830867486.0895</v>
       </c>
       <c r="DQ7" t="n">
-        <v>366459411066.4434</v>
+        <v>366459409385.6646</v>
       </c>
       <c r="DR7" t="n">
-        <v>744134211243.6569</v>
+        <v>744134205933.5284</v>
       </c>
       <c r="DS7" t="n">
-        <v>8662.594444428023</v>
+        <v>8662.594464387623</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2079065629669195</v>
+        <v>0.2079065634459598</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.1010913685546726</v>
+        <v>0.1010913687105926</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.08125915494253289</v>
+        <v>0.08125915482772228</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1886714715329595</v>
+        <v>0.1886714706676113</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.3831171813674702</v>
+        <v>0.3831171786335528</v>
       </c>
       <c r="DY7" t="n">
-        <v>870721364221.4612</v>
+        <v>870721365151.9084</v>
       </c>
       <c r="DZ7" t="n">
-        <v>419198862539.8002</v>
+        <v>419198862850.8844</v>
       </c>
       <c r="EA7" t="n">
-        <v>341894297253.3304</v>
+        <v>341894298151.5792</v>
       </c>
       <c r="EB7" t="n">
-        <v>789928305102.2073</v>
+        <v>789928298919.4536</v>
       </c>
       <c r="EC7" t="n">
-        <v>1587599845353.035</v>
+        <v>1587599858067.389</v>
       </c>
       <c r="ED7" t="n">
-        <v>18678.38580707173</v>
+        <v>18678.38582703133</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.4482905231026068</v>
+        <v>0.4482905235816471</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2158243556364468</v>
+        <v>0.2158243557966084</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.1760241331605952</v>
+        <v>0.1760241336230582</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.4066942510644049</v>
+        <v>0.4066942478812168</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.8173751034434393</v>
+        <v>0.8173751099894192</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.5367129582704392</v>
+        <v>0.5367129576564247</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01549891620548989</v>
+        <v>0.01549891608603728</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.5074381334472992</v>
+        <v>0.5074381419536604</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.5406220347337097</v>
+        <v>0.54062202918424</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.5526131387311798</v>
+        <v>0.5526131357297019</v>
       </c>
       <c r="EO7" t="n">
         <v>1.90980821588117</v>
       </c>
       <c r="EP7" t="n">
-        <v>6.661504687449897e-16</v>
+        <v>0</v>
       </c>
       <c r="EQ7" t="n">
         <v>1.909808215881169</v>
@@ -4624,25 +4624,25 @@
         <v>1.909808215881169</v>
       </c>
       <c r="ET7" t="n">
-        <v>3.561591618961482</v>
+        <v>3.561591627381706</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.1136917637055203</v>
+        <v>0.1136917637515029</v>
       </c>
       <c r="EV7" t="n">
-        <v>3.455958805085983</v>
+        <v>3.455958813133854</v>
       </c>
       <c r="EW7" t="n">
-        <v>3.532612628711295</v>
+        <v>3.53261263797788</v>
       </c>
       <c r="EX7" t="n">
-        <v>3.763627614049165</v>
+        <v>3.763627619404629</v>
       </c>
       <c r="EY7" t="n">
         <v>1.90980821588117</v>
       </c>
       <c r="EZ7" t="n">
-        <v>3.561591618961482</v>
+        <v>3.561591627381706</v>
       </c>
       <c r="FA7" t="n">
         <v>0.2817396149169198</v>
@@ -4780,20 +4780,20 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="AA8" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -4839,31 +4839,31 @@
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="BB8" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="BC8" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="BD8" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="BE8" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="BF8" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="BG8" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="BH8" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="BI8" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
@@ -4875,31 +4875,31 @@
       <c r="BQ8" t="inlineStr"/>
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="BT8" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="BU8" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="BV8" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="BW8" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="BX8" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="BY8" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="BZ8" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="CA8" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
@@ -4929,58 +4929,58 @@
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="CL8" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="CM8" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="CN8" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="CO8" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="CP8" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="CQ8" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="CR8" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="CS8" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="CT8" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="CU8" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="CV8" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="CW8" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="CX8" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="CY8" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="CZ8" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="DA8" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="DB8" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="DC8" t="inlineStr"/>
       <c r="DD8" t="inlineStr"/>
@@ -6159,25 +6159,25 @@
         <v>6454834369.357895</v>
       </c>
       <c r="U2" t="n">
-        <v>27280516.87220764</v>
+        <v>27280517.33257079</v>
       </c>
       <c r="V2" t="n">
-        <v>48479717.22701009</v>
+        <v>48479717.21801874</v>
       </c>
       <c r="W2" t="n">
-        <v>9219468.90634468</v>
+        <v>9219468.906547563</v>
       </c>
       <c r="X2" t="n">
-        <v>84979703.00556241</v>
+        <v>84979703.45713708</v>
       </c>
       <c r="Y2" t="n">
-        <v>1493592513.020832</v>
+        <v>1493592525.333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>1578572216.026394</v>
+        <v>1578572228.79047</v>
       </c>
       <c r="AA2" t="n">
-        <v>8033406585.384289</v>
+        <v>8033406598.148366</v>
       </c>
       <c r="AB2" t="n">
         <v>607000</v>
@@ -6227,190 +6227,190 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>27280516.87220764</v>
+        <v>27280517.33257078</v>
       </c>
       <c r="AT2" t="n">
-        <v>27280516.87220764</v>
+        <v>27280517.33257078</v>
       </c>
       <c r="AU2" t="n">
-        <v>27280516.87220764</v>
+        <v>27280517.33257078</v>
       </c>
       <c r="AV2" t="n">
-        <v>7440140.965147539</v>
+        <v>7440141.09070112</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.313458585529952e-10</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>7440140.965147538</v>
+        <v>7440141.09070112</v>
       </c>
       <c r="AY2" t="n">
-        <v>7440140.965147538</v>
+        <v>7440141.09070112</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7440140.965147538</v>
+        <v>7440141.09070112</v>
       </c>
       <c r="BA2" t="n">
-        <v>43389722.66894829</v>
+        <v>43389722.67015202</v>
       </c>
       <c r="BB2" t="n">
-        <v>10845873.83866951</v>
+        <v>10845873.88005408</v>
       </c>
       <c r="BC2" t="n">
-        <v>36640605.68881893</v>
+        <v>36640604.94464211</v>
       </c>
       <c r="BD2" t="n">
-        <v>125056145.4903053</v>
+        <v>125056144.8864814</v>
       </c>
       <c r="BE2" t="n">
-        <v>13221741.06191184</v>
+        <v>13221741.05945965</v>
       </c>
       <c r="BF2" t="n">
-        <v>11833560.72789499</v>
+        <v>11833560.72822328</v>
       </c>
       <c r="BG2" t="n">
-        <v>2957965.592364413</v>
+        <v>2957965.603651113</v>
       </c>
       <c r="BH2" t="n">
-        <v>9992892.46058698</v>
+        <v>9992892.257629666</v>
       </c>
       <c r="BI2" t="n">
-        <v>34106221.49735599</v>
+        <v>34106221.33267676</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11436921.62041744</v>
+        <v>11436921.63166245</v>
       </c>
       <c r="BK2" t="n">
-        <v>1161536.731161046</v>
+        <v>1161536.708464838</v>
       </c>
       <c r="BL2" t="n">
-        <v>5703350.730239868</v>
+        <v>5703350.782673345</v>
       </c>
       <c r="BM2" t="n">
-        <v>28829752.31851424</v>
+        <v>28829752.70961157</v>
       </c>
       <c r="BN2" t="n">
-        <v>2514400.610821276</v>
+        <v>2514400.610876608</v>
       </c>
       <c r="BO2" t="n">
-        <v>3119160.441932028</v>
+        <v>3119160.444998848</v>
       </c>
       <c r="BP2" t="n">
-        <v>316782.7448621035</v>
+        <v>316782.7386722286</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1555459.290065418</v>
+        <v>1555459.304365458</v>
       </c>
       <c r="BR2" t="n">
-        <v>7862659.723231154</v>
+        <v>7862659.829894064</v>
       </c>
       <c r="BS2" t="n">
-        <v>44848970.77543474</v>
+        <v>44848970.77906384</v>
       </c>
       <c r="BT2" t="n">
-        <v>43719129.32350836</v>
+        <v>43719129.74342863</v>
       </c>
       <c r="BU2" t="n">
-        <v>73428548.12314606</v>
+        <v>73428548.07887214</v>
       </c>
       <c r="BV2" t="n">
-        <v>164361433.4102529</v>
+        <v>164361435.8154987</v>
       </c>
       <c r="BW2" t="n">
-        <v>23176282.63788065</v>
+        <v>23176282.76103738</v>
       </c>
       <c r="BX2" t="n">
-        <v>12231537.48420947</v>
+        <v>12231537.48519923</v>
       </c>
       <c r="BY2" t="n">
-        <v>11923398.90641137</v>
+        <v>11923399.02093508</v>
       </c>
       <c r="BZ2" t="n">
-        <v>20025967.66994892</v>
+        <v>20025967.65787422</v>
       </c>
       <c r="CA2" t="n">
-        <v>44825845.4755235</v>
+        <v>44825846.13149964</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>1493592513.020832</v>
+        <v>1493592525.333333</v>
       </c>
       <c r="CD2" t="n">
-        <v>1493592513.020832</v>
+        <v>1493592525.333333</v>
       </c>
       <c r="CE2" t="n">
-        <v>1493592513.020832</v>
+        <v>1493592525.333333</v>
       </c>
       <c r="CF2" t="n">
-        <v>407343412.6420451</v>
+        <v>407343415.9999999</v>
       </c>
       <c r="CG2" t="n">
-        <v>5.960613494739169e-08</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>407343412.6420451</v>
+        <v>407343415.9999999</v>
       </c>
       <c r="CI2" t="n">
-        <v>407343412.6420451</v>
+        <v>407343415.9999999</v>
       </c>
       <c r="CJ2" t="n">
-        <v>407343412.6420451</v>
+        <v>407343415.9999999</v>
       </c>
       <c r="CK2" t="n">
-        <v>44848970.77543474</v>
+        <v>44848970.77906384</v>
       </c>
       <c r="CL2" t="n">
-        <v>1537311642.34434</v>
+        <v>1537311655.076762</v>
       </c>
       <c r="CM2" t="n">
-        <v>1567021061.143978</v>
+        <v>1567021073.412205</v>
       </c>
       <c r="CN2" t="n">
-        <v>1657953946.431085</v>
+        <v>1657953961.148832</v>
       </c>
       <c r="CO2" t="n">
-        <v>430519695.2799257</v>
+        <v>430519698.7610372</v>
       </c>
       <c r="CP2" t="n">
-        <v>12231537.48420947</v>
+        <v>12231537.48519923</v>
       </c>
       <c r="CQ2" t="n">
-        <v>419266811.5484564</v>
+        <v>419266815.020935</v>
       </c>
       <c r="CR2" t="n">
-        <v>427369380.311994</v>
+        <v>427369383.6578741</v>
       </c>
       <c r="CS2" t="n">
-        <v>452169258.1175686</v>
+        <v>452169262.1314995</v>
       </c>
       <c r="CT2" t="n">
-        <v>44848970.77543474</v>
+        <v>44848970.77906384</v>
       </c>
       <c r="CU2" t="n">
-        <v>7992146011.702236</v>
+        <v>7992146024.434657</v>
       </c>
       <c r="CV2" t="n">
-        <v>8021855430.501873</v>
+        <v>8021855442.7701</v>
       </c>
       <c r="CW2" t="n">
-        <v>8112788315.78898</v>
+        <v>8112788330.506726</v>
       </c>
       <c r="CX2" t="n">
-        <v>2190929068.74117</v>
+        <v>2190929072.222281</v>
       </c>
       <c r="CY2" t="n">
-        <v>12231537.48420947</v>
+        <v>12231537.48519923</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2179676185.0097</v>
+        <v>2179676188.482179</v>
       </c>
       <c r="DA2" t="n">
-        <v>2187778753.773238</v>
+        <v>2187778757.119118</v>
       </c>
       <c r="DB2" t="n">
-        <v>2212578631.578813</v>
+        <v>2212578635.592743</v>
       </c>
       <c r="DC2" t="n">
         <v>3611950332081.179</v>
@@ -6446,91 +6446,91 @@
         <v>0.1175361390579959</v>
       </c>
       <c r="DN2" t="n">
-        <v>883330416635.948</v>
+        <v>883330422721.585</v>
       </c>
       <c r="DO2" t="n">
-        <v>425029159549.5344</v>
+        <v>425029162229.9756</v>
       </c>
       <c r="DP2" t="n">
-        <v>346410449394.7867</v>
+        <v>346410454932.8293</v>
       </c>
       <c r="DQ2" t="n">
-        <v>801425908194.3438</v>
+        <v>801425908141.8352</v>
       </c>
       <c r="DR2" t="n">
-        <v>1608322367865.532</v>
+        <v>1608322425700.608</v>
       </c>
       <c r="DS2" t="n">
-        <v>658.2080522399916</v>
+        <v>658.2080567746654</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.01583217894430326</v>
+        <v>0.01583217905337784</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.007617916901539648</v>
+        <v>0.007617916949581949</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.006208811696852392</v>
+        <v>0.006208811796112284</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.01436418145483482</v>
+        <v>0.0143641814538937</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.02882641313897713</v>
+        <v>0.02882641417557143</v>
       </c>
       <c r="DY2" t="n">
-        <v>4495280748717.126</v>
+        <v>4495280754802.764</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2158048722626.913</v>
+        <v>2158048725314.799</v>
       </c>
       <c r="EA2" t="n">
-        <v>1758510651407.309</v>
+        <v>1758510653712.129</v>
       </c>
       <c r="EB2" t="n">
-        <v>4074419820050.93</v>
+        <v>4074419834111.871</v>
       </c>
       <c r="EC2" t="n">
-        <v>8162620185334.125</v>
+        <v>8162620205200.223</v>
       </c>
       <c r="ED2" t="n">
-        <v>3349.629912160571</v>
+        <v>3349.629916695245</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.08057017835932032</v>
+        <v>0.08057017846839491</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.03867931286377929</v>
+        <v>0.03867931291195503</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.03151827989188114</v>
+        <v>0.03151827993319108</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.07302696982962356</v>
+        <v>0.07302697008164176</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.146300932238647</v>
+        <v>0.1463009325947127</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.8035234481098174</v>
+        <v>0.8035234470065229</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.004377875485563182</v>
+        <v>0.004377875442457095</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.795636973039208</v>
+        <v>0.795636974179303</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.804656032731476</v>
+        <v>0.8046560328903751</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.8076472031092622</v>
+        <v>0.8076472014736442</v>
       </c>
       <c r="EO2" t="n">
         <v>0.5235916405458446</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.11025078124165e-16</v>
+        <v>0</v>
       </c>
       <c r="EQ2" t="n">
         <v>0.5235916405458447</v>
@@ -6542,25 +6542,25 @@
         <v>0.5235916405458447</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.651639421327487</v>
+        <v>0.6516394223628602</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.003637978117080406</v>
+        <v>0.003637978117374785</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.6482925203494223</v>
+        <v>0.6482925213822279</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.6507024355290915</v>
+        <v>0.6507024365242434</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.6580785657072822</v>
+        <v>0.6580785669011298</v>
       </c>
       <c r="EY2" t="n">
         <v>0.5235916405458446</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.651639421327487</v>
+        <v>0.6516394223628602</v>
       </c>
       <c r="FA2" t="n">
         <v>0.0444498351224024</v>
@@ -6721,25 +6721,25 @@
         <v>6129792277.813843</v>
       </c>
       <c r="U3" t="n">
-        <v>6232393.068595886</v>
+        <v>6232393.133159055</v>
       </c>
       <c r="V3" t="n">
-        <v>98402758.15348111</v>
+        <v>98402758.16722739</v>
       </c>
       <c r="W3" t="n">
-        <v>64188241.48060122</v>
+        <v>64188241.46916273</v>
       </c>
       <c r="X3" t="n">
-        <v>168823392.7026782</v>
+        <v>168823392.7695492</v>
       </c>
       <c r="Y3" t="n">
-        <v>1480014745.839844</v>
+        <v>1480014741.333333</v>
       </c>
       <c r="Z3" t="n">
-        <v>1648838138.542522</v>
+        <v>1648838134.102883</v>
       </c>
       <c r="AA3" t="n">
-        <v>7778630416.356365</v>
+        <v>7778630411.916725</v>
       </c>
       <c r="AB3" t="n">
         <v>5709690</v>
@@ -6793,190 +6793,190 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>6232393.068595886</v>
+        <v>6232393.133159054</v>
       </c>
       <c r="AT3" t="n">
-        <v>6232393.068595886</v>
+        <v>6232393.133159054</v>
       </c>
       <c r="AU3" t="n">
-        <v>6232393.068595886</v>
+        <v>6232393.133159054</v>
       </c>
       <c r="AV3" t="n">
-        <v>1699743.564162515</v>
+        <v>1699743.581770651</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.656729292764976e-10</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1699743.564162514</v>
+        <v>1699743.581770651</v>
       </c>
       <c r="AY3" t="n">
-        <v>1699743.564162514</v>
+        <v>1699743.581770651</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1699743.564162514</v>
+        <v>1699743.581770651</v>
       </c>
       <c r="BA3" t="n">
-        <v>88071231.25828227</v>
+        <v>88071231.26673479</v>
       </c>
       <c r="BB3" t="n">
-        <v>22014647.92551727</v>
+        <v>22014647.89350162</v>
       </c>
       <c r="BC3" t="n">
-        <v>74372062.97669983</v>
+        <v>74372063.08885901</v>
       </c>
       <c r="BD3" t="n">
-        <v>253835422.4062179</v>
+        <v>253835424.1475731</v>
       </c>
       <c r="BE3" t="n">
-        <v>26837115.8600403</v>
+        <v>26837115.86378929</v>
       </c>
       <c r="BF3" t="n">
-        <v>24019426.70680426</v>
+        <v>24019426.70910949</v>
       </c>
       <c r="BG3" t="n">
-        <v>6003994.888777438</v>
+        <v>6003994.880045897</v>
       </c>
       <c r="BH3" t="n">
-        <v>20283289.90273631</v>
+        <v>20283289.93332518</v>
       </c>
       <c r="BI3" t="n">
-        <v>69227842.47442307</v>
+        <v>69227842.94933811</v>
       </c>
       <c r="BJ3" t="n">
-        <v>79626700.28814636</v>
+        <v>79626700.27941401</v>
       </c>
       <c r="BK3" t="n">
-        <v>8086908.141526403</v>
+        <v>8086908.20197766</v>
       </c>
       <c r="BL3" t="n">
-        <v>39708150.42577565</v>
+        <v>39708150.32106495</v>
       </c>
       <c r="BM3" t="n">
-        <v>200719932.1889852</v>
+        <v>200719927.2733129</v>
       </c>
       <c r="BN3" t="n">
-        <v>17505884.04016396</v>
+        <v>17505884.03704438</v>
       </c>
       <c r="BO3" t="n">
-        <v>21716372.8058581</v>
+        <v>21716372.80347655</v>
       </c>
       <c r="BP3" t="n">
-        <v>2205520.402234473</v>
+        <v>2205520.41872118</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10829495.57066609</v>
+        <v>10829495.54210862</v>
       </c>
       <c r="BR3" t="n">
-        <v>54741799.68790506</v>
+        <v>54741798.34726715</v>
       </c>
       <c r="BS3" t="n">
-        <v>118609062.8755984</v>
+        <v>118609062.874373</v>
       </c>
       <c r="BT3" t="n">
-        <v>54870275.22285107</v>
+        <v>54870275.06345219</v>
       </c>
       <c r="BU3" t="n">
-        <v>138419121.1614785</v>
+        <v>138419120.7181813</v>
       </c>
       <c r="BV3" t="n">
-        <v>381881135.9283221</v>
+        <v>381881138.6823851</v>
       </c>
       <c r="BW3" t="n">
-        <v>46042743.46436678</v>
+        <v>46042743.48260432</v>
       </c>
       <c r="BX3" t="n">
-        <v>32347926.23879957</v>
+        <v>32347926.23846535</v>
       </c>
       <c r="BY3" t="n">
-        <v>14964620.51532302</v>
+        <v>14964620.4718506</v>
       </c>
       <c r="BZ3" t="n">
-        <v>37750669.40767596</v>
+        <v>37750669.28677671</v>
       </c>
       <c r="CA3" t="n">
-        <v>104149400.7077242</v>
+        <v>104149401.4588323</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>1480014745.839844</v>
+        <v>1480014741.333333</v>
       </c>
       <c r="CD3" t="n">
-        <v>1480014745.839844</v>
+        <v>1480014741.333333</v>
       </c>
       <c r="CE3" t="n">
-        <v>1480014745.839844</v>
+        <v>1480014741.333333</v>
       </c>
       <c r="CF3" t="n">
-        <v>403640385.2290481</v>
+        <v>403640383.9999999</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.192122698947834e-07</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>403640385.2290483</v>
+        <v>403640383.9999999</v>
       </c>
       <c r="CI3" t="n">
-        <v>403640385.2290483</v>
+        <v>403640383.9999999</v>
       </c>
       <c r="CJ3" t="n">
-        <v>403640385.2290483</v>
+        <v>403640383.9999999</v>
       </c>
       <c r="CK3" t="n">
-        <v>118609062.8755984</v>
+        <v>118609062.874373</v>
       </c>
       <c r="CL3" t="n">
-        <v>1534885021.062695</v>
+        <v>1534885016.396785</v>
       </c>
       <c r="CM3" t="n">
-        <v>1618433867.001322</v>
+        <v>1618433862.051515</v>
       </c>
       <c r="CN3" t="n">
-        <v>1861895881.768166</v>
+        <v>1861895880.015718</v>
       </c>
       <c r="CO3" t="n">
-        <v>449683128.693415</v>
+        <v>449683127.4826043</v>
       </c>
       <c r="CP3" t="n">
-        <v>32347926.23879957</v>
+        <v>32347926.23846535</v>
       </c>
       <c r="CQ3" t="n">
-        <v>418605005.7443713</v>
+        <v>418605004.4718506</v>
       </c>
       <c r="CR3" t="n">
-        <v>441391054.6367242</v>
+        <v>441391053.2867767</v>
       </c>
       <c r="CS3" t="n">
-        <v>507789785.9367725</v>
+        <v>507789785.4588323</v>
       </c>
       <c r="CT3" t="n">
-        <v>118609062.8755984</v>
+        <v>118609062.874373</v>
       </c>
       <c r="CU3" t="n">
-        <v>7664677298.876537</v>
+        <v>7664677294.210629</v>
       </c>
       <c r="CV3" t="n">
-        <v>7748226144.815166</v>
+        <v>7748226139.865357</v>
       </c>
       <c r="CW3" t="n">
-        <v>7991688159.582008</v>
+        <v>7991688157.829561</v>
       </c>
       <c r="CX3" t="n">
-        <v>2121444659.006281</v>
+        <v>2121444657.79547</v>
       </c>
       <c r="CY3" t="n">
-        <v>32347926.23879957</v>
+        <v>32347926.23846535</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2090366536.057237</v>
+        <v>2090366534.784717</v>
       </c>
       <c r="DA3" t="n">
-        <v>2113152584.94959</v>
+        <v>2113152583.599643</v>
       </c>
       <c r="DB3" t="n">
-        <v>2179551316.249639</v>
+        <v>2179551315.771698</v>
       </c>
       <c r="DC3" t="n">
         <v>3430065586792.886</v>
@@ -7012,85 +7012,85 @@
         <v>0.1653071753235437</v>
       </c>
       <c r="DN3" t="n">
-        <v>922526954315.0972</v>
+        <v>922526945498.562</v>
       </c>
       <c r="DO3" t="n">
-        <v>448773359868.4952</v>
+        <v>448773356071.9002</v>
       </c>
       <c r="DP3" t="n">
-        <v>359559004315.9681</v>
+        <v>359558997826.9257</v>
       </c>
       <c r="DQ3" t="n">
-        <v>837074819319.2734</v>
+        <v>837074821512.5846</v>
       </c>
       <c r="DR3" t="n">
-        <v>1700590798058.918</v>
+        <v>1700590801241.214</v>
       </c>
       <c r="DS3" t="n">
-        <v>167.0235968258039</v>
+        <v>167.0235952295693</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.02448816212469831</v>
+        <v>0.0244881618906664</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.01191253517558651</v>
+        <v>0.0119125350748072</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.009544370654862322</v>
+        <v>0.009544370482612911</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.02221986446044968</v>
+        <v>0.02221986451867037</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.04514160044413498</v>
+        <v>0.04514160052860791</v>
       </c>
       <c r="DY3" t="n">
-        <v>4352592541107.982</v>
+        <v>4352592532291.447</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2090585701692.759</v>
+        <v>2090585697868.643</v>
       </c>
       <c r="EA3" t="n">
-        <v>1710352644899.156</v>
+        <v>1710352638241.746</v>
       </c>
       <c r="EB3" t="n">
-        <v>3945790964350.5</v>
+        <v>3945790954087.745</v>
       </c>
       <c r="EC3" t="n">
-        <v>7890312453929.578</v>
+        <v>7890312421641</v>
       </c>
       <c r="ED3" t="n">
-        <v>788.0373124411848</v>
+        <v>788.0373108449502</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1155380786554223</v>
+        <v>0.1155380784213904</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.05549388162499423</v>
+        <v>0.05549388152348438</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.04540072532600652</v>
+        <v>0.04540072514928784</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.1047396700911804</v>
+        <v>0.1047396698187591</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2094456424092276</v>
+        <v>0.2094456415521383</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.788204057711109</v>
+        <v>0.7882040593163616</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.01145632532749916</v>
+        <v>0.01145632535760204</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.767020949999681</v>
+        <v>0.7670209534617247</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.7911220134882646</v>
+        <v>0.7911220142438298</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.7997456413867854</v>
+        <v>0.7997456434931994</v>
       </c>
       <c r="EO3" t="n">
         <v>0.253717746790159</v>
@@ -7108,25 +7108,25 @@
         <v>0.253717746790159</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.3219646756211449</v>
+        <v>0.3219646754373841</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.004909338329556203</v>
+        <v>0.00490933832950548</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.3172480511587892</v>
+        <v>0.3172480509656629</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.3207062148253118</v>
+        <v>0.3207062146204347</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.3307833318002553</v>
+        <v>0.33078333172772</v>
       </c>
       <c r="EY3" t="n">
         <v>0.253717746790159</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.3219646756211449</v>
+        <v>0.3219646754373841</v>
       </c>
       <c r="FA3" t="n">
         <v>0.3382011217138648</v>
@@ -7287,25 +7287,25 @@
         <v>1884391381.267578</v>
       </c>
       <c r="U4" t="n">
-        <v>49788.484375</v>
+        <v>49788.48476497281</v>
       </c>
       <c r="V4" t="n">
-        <v>32842949.57846042</v>
+        <v>32842949.57532942</v>
       </c>
       <c r="W4" t="n">
-        <v>16159570.20155462</v>
+        <v>16159570.20146285</v>
       </c>
       <c r="X4" t="n">
-        <v>49052308.26439004</v>
+        <v>49052308.26155724</v>
       </c>
       <c r="Y4" t="n">
-        <v>191836191</v>
+        <v>191836190.3333333</v>
       </c>
       <c r="Z4" t="n">
-        <v>240888499.2643901</v>
+        <v>240888498.5948905</v>
       </c>
       <c r="AA4" t="n">
-        <v>2125279880.531968</v>
+        <v>2125279879.862469</v>
       </c>
       <c r="AB4" t="n">
         <v>2744750</v>
@@ -7355,190 +7355,190 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>49788.484375</v>
+        <v>49788.4847649728</v>
       </c>
       <c r="AT4" t="n">
-        <v>49788.484375</v>
+        <v>49788.4847649728</v>
       </c>
       <c r="AU4" t="n">
-        <v>49788.484375</v>
+        <v>49788.4847649728</v>
       </c>
       <c r="AV4" t="n">
-        <v>13578.67755681818</v>
+        <v>13578.6776631744</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.819034879986319e-12</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>13578.67755681818</v>
+        <v>13578.6776631744</v>
       </c>
       <c r="AY4" t="n">
-        <v>13578.67755681818</v>
+        <v>13578.6776631744</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13578.67755681818</v>
+        <v>13578.6776631744</v>
       </c>
       <c r="BA4" t="n">
-        <v>29394694.423739</v>
+        <v>29394694.43137913</v>
       </c>
       <c r="BB4" t="n">
-        <v>7347619.020544434</v>
+        <v>7347618.950438184</v>
       </c>
       <c r="BC4" t="n">
-        <v>24822453.75732422</v>
+        <v>24822453.79432983</v>
       </c>
       <c r="BD4" t="n">
-        <v>84720226.99082029</v>
+        <v>84720227.26785314</v>
       </c>
       <c r="BE4" t="n">
-        <v>8957168.066852842</v>
+        <v>8957168.06599893</v>
       </c>
       <c r="BF4" t="n">
-        <v>8016734.842837909</v>
+        <v>8016734.84492158</v>
       </c>
       <c r="BG4" t="n">
-        <v>2003896.096512118</v>
+        <v>2003896.077392232</v>
       </c>
       <c r="BH4" t="n">
-        <v>6769760.115633877</v>
+        <v>6769760.125726317</v>
       </c>
       <c r="BI4" t="n">
-        <v>23105516.4520419</v>
+        <v>23105516.52759631</v>
       </c>
       <c r="BJ4" t="n">
-        <v>20046245.58670358</v>
+        <v>20046245.59926921</v>
       </c>
       <c r="BK4" t="n">
-        <v>2035901.853930617</v>
+        <v>2035901.869432354</v>
       </c>
       <c r="BL4" t="n">
-        <v>9996638.574159622</v>
+        <v>9996638.449610088</v>
       </c>
       <c r="BM4" t="n">
-        <v>50531805.87258451</v>
+        <v>50531805.84739778</v>
       </c>
       <c r="BN4" t="n">
-        <v>4407155.509514897</v>
+        <v>4407155.50948987</v>
       </c>
       <c r="BO4" t="n">
-        <v>5467157.887282793</v>
+        <v>5467157.890709784</v>
       </c>
       <c r="BP4" t="n">
-        <v>555245.9601628953</v>
+        <v>555245.9643906421</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2726355.974770806</v>
+        <v>2726355.940802751</v>
       </c>
       <c r="BR4" t="n">
-        <v>13781401.60161396</v>
+        <v>13781401.59474485</v>
       </c>
       <c r="BS4" t="n">
-        <v>35545413.96296628</v>
+        <v>35545413.97475266</v>
       </c>
       <c r="BT4" t="n">
-        <v>14810182.73056779</v>
+        <v>14810182.60361408</v>
       </c>
       <c r="BU4" t="n">
-        <v>40076840.85843658</v>
+        <v>40076840.75855632</v>
       </c>
       <c r="BV4" t="n">
-        <v>113401501.9458874</v>
+        <v>113401501.6112094</v>
       </c>
       <c r="BW4" t="n">
-        <v>13377902.25392455</v>
+        <v>13377902.25315197</v>
       </c>
       <c r="BX4" t="n">
-        <v>9694203.808081713</v>
+        <v>9694203.81129618</v>
       </c>
       <c r="BY4" t="n">
-        <v>4039140.744700306</v>
+        <v>4039140.710076566</v>
       </c>
       <c r="BZ4" t="n">
-        <v>10930047.50684634</v>
+        <v>10930047.47960627</v>
       </c>
       <c r="CA4" t="n">
-        <v>30927682.34887837</v>
+        <v>30927682.25760255</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>191836191</v>
+        <v>191836190.3333333</v>
       </c>
       <c r="CD4" t="n">
-        <v>191836191</v>
+        <v>191836190.3333333</v>
       </c>
       <c r="CE4" t="n">
-        <v>191836191</v>
+        <v>191836190.3333333</v>
       </c>
       <c r="CF4" t="n">
-        <v>52318961.18181816</v>
+        <v>52318960.99999999</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.490153373684792e-08</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>52318961.18181818</v>
+        <v>52318960.99999999</v>
       </c>
       <c r="CI4" t="n">
-        <v>52318961.18181818</v>
+        <v>52318960.99999999</v>
       </c>
       <c r="CJ4" t="n">
-        <v>52318961.18181818</v>
+        <v>52318960.99999999</v>
       </c>
       <c r="CK4" t="n">
-        <v>35545413.96296628</v>
+        <v>35545413.97475266</v>
       </c>
       <c r="CL4" t="n">
-        <v>206646373.7305678</v>
+        <v>206646372.9369474</v>
       </c>
       <c r="CM4" t="n">
-        <v>231913031.8584366</v>
+        <v>231913031.0918896</v>
       </c>
       <c r="CN4" t="n">
-        <v>305237692.9458873</v>
+        <v>305237691.9445427</v>
       </c>
       <c r="CO4" t="n">
-        <v>65696863.43574274</v>
+        <v>65696863.25315197</v>
       </c>
       <c r="CP4" t="n">
-        <v>9694203.808081713</v>
+        <v>9694203.81129618</v>
       </c>
       <c r="CQ4" t="n">
-        <v>56358101.92651848</v>
+        <v>56358101.71007655</v>
       </c>
       <c r="CR4" t="n">
-        <v>63249008.68866452</v>
+        <v>63249008.47960626</v>
       </c>
       <c r="CS4" t="n">
-        <v>83246643.53069654</v>
+        <v>83246643.25760254</v>
       </c>
       <c r="CT4" t="n">
-        <v>35545413.96296629</v>
+        <v>35545413.97475266</v>
       </c>
       <c r="CU4" t="n">
-        <v>2091037754.998146</v>
+        <v>2091037754.204525</v>
       </c>
       <c r="CV4" t="n">
-        <v>2116304413.126015</v>
+        <v>2116304412.359468</v>
       </c>
       <c r="CW4" t="n">
-        <v>2189629074.213466</v>
+        <v>2189629073.212121</v>
       </c>
       <c r="CX4" t="n">
-        <v>579621785.5996276</v>
+        <v>579621785.4170368</v>
       </c>
       <c r="CY4" t="n">
-        <v>9694203.808081714</v>
+        <v>9694203.811296182</v>
       </c>
       <c r="CZ4" t="n">
-        <v>570283024.0904034</v>
+        <v>570283023.8739614</v>
       </c>
       <c r="DA4" t="n">
-        <v>577173930.8525494</v>
+        <v>577173930.6434911</v>
       </c>
       <c r="DB4" t="n">
-        <v>597171565.6945814</v>
+        <v>597171565.4214876</v>
       </c>
       <c r="DC4" t="n">
         <v>1054454334099.734</v>
@@ -7574,91 +7574,91 @@
         <v>1.558601053486631</v>
       </c>
       <c r="DN4" t="n">
-        <v>134769896872.2909</v>
+        <v>134769896544.5565</v>
       </c>
       <c r="DO4" t="n">
-        <v>68289708300.26821</v>
+        <v>68289708152.74732</v>
       </c>
       <c r="DP4" t="n">
-        <v>51889524587.5043</v>
+        <v>51889524967.21423</v>
       </c>
       <c r="DQ4" t="n">
-        <v>121289659900.502</v>
+        <v>121289659519.9481</v>
       </c>
       <c r="DR4" t="n">
-        <v>256496638439.1376</v>
+        <v>256496636881.5753</v>
       </c>
       <c r="DS4" t="n">
-        <v>115.2407030415529</v>
+        <v>115.2407027613096</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1097205399757891</v>
+        <v>0.1097205397089698</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.05559686431009722</v>
+        <v>0.05559686418999568</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.04224494333644122</v>
+        <v>0.04224494364557538</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09874584225862863</v>
+        <v>0.09874584194880739</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2088222245816914</v>
+        <v>0.2088222233136294</v>
       </c>
       <c r="DY4" t="n">
-        <v>1189224230972.025</v>
+        <v>1189224230644.291</v>
       </c>
       <c r="DZ4" t="n">
-        <v>571293724880.6747</v>
+        <v>571293724705.7419</v>
       </c>
       <c r="EA4" t="n">
-        <v>467582308709.0741</v>
+        <v>467582308721.1674</v>
       </c>
       <c r="EB4" t="n">
-        <v>1077486751786.973</v>
+        <v>1077486750844.959</v>
       </c>
       <c r="EC4" t="n">
-        <v>2155227944097.163</v>
+        <v>2155227936657.432</v>
       </c>
       <c r="ED4" t="n">
-        <v>1016.896500122228</v>
+        <v>1016.896499841985</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.9681859807178549</v>
+        <v>0.9681859804510359</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.465108732984237</v>
+        <v>0.4651087328418186</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.3806739085309328</v>
+        <v>0.3806739085407783</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.8772168782977865</v>
+        <v>0.8772168775308626</v>
       </c>
       <c r="EI4" t="n">
-        <v>1.754640904870129</v>
+        <v>1.754640898813203</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.8868902144652527</v>
+        <v>0.88689021470715</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01406773438325916</v>
+        <v>0.01406773444693625</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.8605984462576545</v>
+        <v>0.8605984484793011</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.8904160340724832</v>
+        <v>0.8904160341670663</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.9011752081980172</v>
+        <v>0.901175207107206</v>
       </c>
       <c r="EO4" t="n">
         <v>4.616159740574195</v>
       </c>
       <c r="EP4" t="n">
-        <v>8.882006249933197e-16</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="n">
         <v>4.616159740574196</v>
@@ -7670,25 +7670,25 @@
         <v>4.616159740574196</v>
       </c>
       <c r="ET4" t="n">
-        <v>5.206259973108488</v>
+        <v>5.206259971468427</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0870749625205325</v>
+        <v>0.08707496254940539</v>
       </c>
       <c r="EV4" t="n">
-        <v>5.122377652857909</v>
+        <v>5.122377650913791</v>
       </c>
       <c r="EW4" t="n">
-        <v>5.184272931719916</v>
+        <v>5.18427292984212</v>
       </c>
       <c r="EX4" t="n">
-        <v>5.363895037757916</v>
+        <v>5.363895035304941</v>
       </c>
       <c r="EY4" t="n">
         <v>4.616159740574195</v>
       </c>
       <c r="EZ4" t="n">
-        <v>5.206259973108488</v>
+        <v>5.206259971468427</v>
       </c>
       <c r="FA4" t="n">
         <v>0.4990399141401116</v>
@@ -7845,25 +7845,25 @@
         <v>294819064.3126068</v>
       </c>
       <c r="U5" t="n">
-        <v>36827.84501492977</v>
+        <v>36827.8464130808</v>
       </c>
       <c r="V5" t="n">
-        <v>119287649.6478837</v>
+        <v>119287649.6681324</v>
       </c>
       <c r="W5" t="n">
-        <v>11092480.65868703</v>
+        <v>11092480.66049321</v>
       </c>
       <c r="X5" t="n">
-        <v>130416958.1515856</v>
+        <v>130416958.1750387</v>
       </c>
       <c r="Y5" t="n">
-        <v>564111444.2617167</v>
+        <v>564111449.2929668</v>
       </c>
       <c r="Z5" t="n">
-        <v>694528402.4133022</v>
+        <v>694528407.4680054</v>
       </c>
       <c r="AA5" t="n">
-        <v>989347466.725909</v>
+        <v>989347471.7806123</v>
       </c>
       <c r="AB5" t="n">
         <v>108970</v>
@@ -7909,190 +7909,190 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>36827.84501492977</v>
+        <v>36827.84641308079</v>
       </c>
       <c r="AT5" t="n">
-        <v>36827.84501492977</v>
+        <v>36827.84641308079</v>
       </c>
       <c r="AU5" t="n">
-        <v>36827.84501492977</v>
+        <v>36827.84641308079</v>
       </c>
       <c r="AV5" t="n">
-        <v>10043.95773134448</v>
+        <v>10043.9581126584</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.638069759972638e-12</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>10043.95773134448</v>
+        <v>10043.9581126584</v>
       </c>
       <c r="AY5" t="n">
-        <v>10043.95773134448</v>
+        <v>10043.9581126584</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10043.95773134448</v>
+        <v>10043.9581126584</v>
       </c>
       <c r="BA5" t="n">
-        <v>106763370.9616713</v>
+        <v>106763371.0361408</v>
       </c>
       <c r="BB5" t="n">
-        <v>26687011.81995392</v>
+        <v>26687012.17728584</v>
       </c>
       <c r="BC5" t="n">
-        <v>90156707.13522339</v>
+        <v>90156706.70290956</v>
       </c>
       <c r="BD5" t="n">
-        <v>307709167.710852</v>
+        <v>307709171.0947785</v>
       </c>
       <c r="BE5" t="n">
-        <v>32532995.35851373</v>
+        <v>32532995.36403611</v>
       </c>
       <c r="BF5" t="n">
-        <v>29117282.98954672</v>
+        <v>29117283.00985657</v>
       </c>
       <c r="BG5" t="n">
-        <v>7278275.950896523</v>
+        <v>7278276.048350682</v>
       </c>
       <c r="BH5" t="n">
-        <v>24588192.85506092</v>
+        <v>24588192.73715715</v>
       </c>
       <c r="BI5" t="n">
-        <v>83920682.10295962</v>
+        <v>83920683.02584869</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13760427.32767115</v>
+        <v>13760427.34139434</v>
       </c>
       <c r="BK5" t="n">
-        <v>1397512.560885367</v>
+        <v>1397512.547165147</v>
       </c>
       <c r="BL5" t="n">
-        <v>6862033.944714427</v>
+        <v>6862033.908686785</v>
       </c>
       <c r="BM5" t="n">
-        <v>34686756.854405</v>
+        <v>34686756.64723531</v>
       </c>
       <c r="BN5" t="n">
-        <v>3025221.997823736</v>
+        <v>3025221.998316329</v>
       </c>
       <c r="BO5" t="n">
-        <v>3752843.816637585</v>
+        <v>3752843.820380275</v>
       </c>
       <c r="BP5" t="n">
-        <v>381139.7893323728</v>
+        <v>381139.7855904946</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1871463.803103935</v>
+        <v>1871463.793278214</v>
       </c>
       <c r="BR5" t="n">
-        <v>9460024.596655907</v>
+        <v>9460024.540155083</v>
       </c>
       <c r="BS5" t="n">
-        <v>107618420.1978054</v>
+        <v>107618420.2751312</v>
       </c>
       <c r="BT5" t="n">
-        <v>34630081.96246345</v>
+        <v>34630082.39488047</v>
       </c>
       <c r="BU5" t="n">
-        <v>101970736.5606966</v>
+        <v>101970736.6894848</v>
       </c>
       <c r="BV5" t="n">
-        <v>320260095.6661233</v>
+        <v>320260092.4809669</v>
       </c>
       <c r="BW5" t="n">
-        <v>35568261.31406881</v>
+        <v>35568261.3204651</v>
       </c>
       <c r="BX5" t="n">
-        <v>29350478.2357651</v>
+        <v>29350478.25685398</v>
       </c>
       <c r="BY5" t="n">
-        <v>9444567.807944577</v>
+        <v>9444567.925876491</v>
       </c>
       <c r="BZ5" t="n">
-        <v>27810200.88018998</v>
+        <v>27810200.91531403</v>
       </c>
       <c r="CA5" t="n">
-        <v>87343662.45439725</v>
+        <v>87343661.58571824</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.192122698947834e-07</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>564111444.2617166</v>
+        <v>564111449.2929668</v>
       </c>
       <c r="CD5" t="n">
-        <v>564111444.2617166</v>
+        <v>564111449.2929668</v>
       </c>
       <c r="CE5" t="n">
-        <v>564111444.2617166</v>
+        <v>564111449.2929668</v>
       </c>
       <c r="CF5" t="n">
-        <v>153848575.7077408</v>
+        <v>153848577.0799</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.980306747369585e-08</v>
+        <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>153848575.7077409</v>
+        <v>153848577.0799</v>
       </c>
       <c r="CI5" t="n">
-        <v>153848575.7077409</v>
+        <v>153848577.0799</v>
       </c>
       <c r="CJ5" t="n">
-        <v>153848575.7077409</v>
+        <v>153848577.0799</v>
       </c>
       <c r="CK5" t="n">
-        <v>107618420.1978054</v>
+        <v>107618420.2751313</v>
       </c>
       <c r="CL5" t="n">
-        <v>598741526.2241801</v>
+        <v>598741531.6878474</v>
       </c>
       <c r="CM5" t="n">
-        <v>666082180.8224132</v>
+        <v>666082185.9824517</v>
       </c>
       <c r="CN5" t="n">
-        <v>884371539.9278399</v>
+        <v>884371541.7739338</v>
       </c>
       <c r="CO5" t="n">
-        <v>189416837.0218097</v>
+        <v>189416838.4003651</v>
       </c>
       <c r="CP5" t="n">
-        <v>29350478.2357651</v>
+        <v>29350478.25685398</v>
       </c>
       <c r="CQ5" t="n">
-        <v>163293143.5156855</v>
+        <v>163293145.0057765</v>
       </c>
       <c r="CR5" t="n">
-        <v>181658776.5879309</v>
+        <v>181658777.9952141</v>
       </c>
       <c r="CS5" t="n">
-        <v>241192238.1621381</v>
+        <v>241192238.6656183</v>
       </c>
       <c r="CT5" t="n">
-        <v>107618420.1978054</v>
+        <v>107618420.2751312</v>
       </c>
       <c r="CU5" t="n">
-        <v>893560590.5367869</v>
+        <v>893560596.0004542</v>
       </c>
       <c r="CV5" t="n">
-        <v>960901245.13502</v>
+        <v>960901250.2950585</v>
       </c>
       <c r="CW5" t="n">
-        <v>1179190604.240447</v>
+        <v>1179190606.08654</v>
       </c>
       <c r="CX5" t="n">
-        <v>269822036.3797933</v>
+        <v>269822037.7583488</v>
       </c>
       <c r="CY5" t="n">
-        <v>29350478.2357651</v>
+        <v>29350478.25685398</v>
       </c>
       <c r="CZ5" t="n">
-        <v>243698342.8736691</v>
+        <v>243698344.3637602</v>
       </c>
       <c r="DA5" t="n">
-        <v>262063975.9459145</v>
+        <v>262063977.3531978</v>
       </c>
       <c r="DB5" t="n">
-        <v>321597437.5201218</v>
+        <v>321597438.0236019</v>
       </c>
       <c r="DC5" t="n">
         <v>164972756168.3519</v>
@@ -8128,85 +8128,85 @@
         <v>0.3249790573107983</v>
       </c>
       <c r="DN5" t="n">
-        <v>388681890201.8808</v>
+        <v>388681892855.9197</v>
       </c>
       <c r="DO5" t="n">
-        <v>198226088850.9051</v>
+        <v>198226089723.0193</v>
       </c>
       <c r="DP5" t="n">
-        <v>149909914623.2047</v>
+        <v>149909915571.956</v>
       </c>
       <c r="DQ5" t="n">
-        <v>349538764401.2158</v>
+        <v>349538767483.2842</v>
       </c>
       <c r="DR5" t="n">
-        <v>745239035569.6858</v>
+        <v>745239037962.079</v>
       </c>
       <c r="DS5" t="n">
-        <v>5347.079680961893</v>
+        <v>5347.079717473389</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.4217210687396571</v>
+        <v>0.4217210716192976</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2150759275119976</v>
+        <v>0.2150759284582443</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.1626527270841771</v>
+        <v>0.1626527281135753</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.3792506545974049</v>
+        <v>0.3792506579414588</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.8085866886767509</v>
+        <v>0.8085866912725049</v>
       </c>
       <c r="DY5" t="n">
-        <v>553654646370.2328</v>
+        <v>553654649024.2717</v>
       </c>
       <c r="DZ5" t="n">
-        <v>274181300353.7704</v>
+        <v>274181301283.1808</v>
       </c>
       <c r="EA5" t="n">
-        <v>215222810121.4353</v>
+        <v>215222810283.0555</v>
       </c>
       <c r="EB5" t="n">
-        <v>501571102274.2421</v>
+        <v>501571100268.4344</v>
       </c>
       <c r="EC5" t="n">
-        <v>1046208256867.832</v>
+        <v>1046208255997.641</v>
       </c>
       <c r="ED5" t="n">
-        <v>7616.602637027334</v>
+        <v>7616.602673538831</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.6007170260972495</v>
+        <v>0.6007170289768901</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.2974875699857381</v>
+        <v>0.2974875709941512</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2335174233469466</v>
+        <v>0.233517423522305</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.5442062175579018</v>
+        <v>0.5442062153815942</v>
       </c>
       <c r="EI5" t="n">
-        <v>1.13513923682267</v>
+        <v>1.13513923587851</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.3006767672860454</v>
+        <v>0.3006767657736584</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02575906582983722</v>
+        <v>0.02575906547703257</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2500181536287595</v>
+        <v>0.2500181560605287</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.3068151518194477</v>
+        <v>0.3068151516591835</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.329937405225431</v>
+        <v>0.3299374067605924</v>
       </c>
       <c r="EO5" t="n">
         <v>1.43644833212014</v>
@@ -8224,25 +8224,25 @@
         <v>1.43644833212014</v>
       </c>
       <c r="ET5" t="n">
-        <v>4.820402377231709</v>
+        <v>4.820402401859763</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.5243497416253469</v>
+        <v>0.524349742002102</v>
       </c>
       <c r="EV5" t="n">
-        <v>4.35369952386749</v>
+        <v>4.353699550488141</v>
       </c>
       <c r="EW5" t="n">
-        <v>4.681803716203378</v>
+        <v>4.681803741344658</v>
       </c>
       <c r="EX5" t="n">
-        <v>5.745376000911819</v>
+        <v>5.745376009906552</v>
       </c>
       <c r="EY5" t="n">
         <v>1.43644833212014</v>
       </c>
       <c r="EZ5" t="n">
-        <v>4.820402377231709</v>
+        <v>4.820402401859763</v>
       </c>
       <c r="FA5" t="n">
         <v>0.1266353607684635</v>
@@ -8380,20 +8380,20 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="AA6" t="n">
-        <v>1738.098639987183</v>
+        <v>1738.098640034579</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -8439,31 +8439,31 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="BB6" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="BC6" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="BD6" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="BE6" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="BF6" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="BG6" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="BH6" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="BI6" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
@@ -8475,31 +8475,31 @@
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="BT6" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="BU6" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="BV6" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="BW6" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="BX6" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="BY6" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="BZ6" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="CA6" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -8529,58 +8529,58 @@
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="CL6" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="CM6" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="CN6" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="CO6" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="CP6" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="CQ6" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="CR6" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="CS6" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="CT6" t="n">
-        <v>1555.611750242108</v>
+        <v>1555.611754608969</v>
       </c>
       <c r="CU6" t="n">
-        <v>388.8471389770508</v>
+        <v>388.8471245847539</v>
       </c>
       <c r="CV6" t="n">
-        <v>1313.641845703125</v>
+        <v>1313.641854343502</v>
       </c>
       <c r="CW6" t="n">
-        <v>4483.522656249998</v>
+        <v>4483.522756076913</v>
       </c>
       <c r="CX6" t="n">
-        <v>474.0269018146861</v>
+        <v>474.0269018276124</v>
       </c>
       <c r="CY6" t="n">
-        <v>424.2577500660294</v>
+        <v>424.2577512569915</v>
       </c>
       <c r="CZ6" t="n">
-        <v>106.0492197210138</v>
+        <v>106.049215795842</v>
       </c>
       <c r="DA6" t="n">
-        <v>358.2659579190341</v>
+        <v>358.2659602755004</v>
       </c>
       <c r="DB6" t="n">
-        <v>1222.77890625</v>
+        <v>1222.778933475521</v>
       </c>
       <c r="DC6" t="inlineStr"/>
       <c r="DD6" t="inlineStr"/>
